--- a/Packages/cn.etetet.wow/Luban/Datas/Unit.xlsx
+++ b/Packages/cn.etetet.wow/Luban/Datas/Unit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12360"/>
+    <workbookView windowWidth="21195" windowHeight="12142"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="62">
   <si>
     <t>##var</t>
   </si>
@@ -167,6 +167,9 @@
   </si>
   <si>
     <t>德鲁伊</t>
+  </si>
+  <si>
+    <t>300000</t>
   </si>
   <si>
     <t>猎人</t>
@@ -1212,7 +1215,7 @@
     <col min="21" max="21" width="5.24778761061947" customWidth="1"/>
     <col min="22" max="23" width="6.17699115044248" customWidth="1"/>
     <col min="24" max="24" width="5.24778761061947" customWidth="1"/>
-    <col min="25" max="25" width="2.46017699115044" customWidth="1"/>
+    <col min="25" max="25" width="7.10619469026549" customWidth="1"/>
     <col min="26" max="26" width="6.17699115044248" customWidth="1"/>
     <col min="27" max="29" width="5.24778761061947" customWidth="1"/>
     <col min="30" max="30" width="6.17699115044248" customWidth="1"/>
@@ -1797,8 +1800,8 @@
       <c r="X8" s="10">
         <v>1009</v>
       </c>
-      <c r="Y8" s="8">
-        <v>3</v>
+      <c r="Y8" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="Z8" s="10">
         <v>10021</v>
@@ -1842,7 +1845,7 @@
         <v>45</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H9" s="4">
         <v>1010</v>
@@ -1895,8 +1898,8 @@
       <c r="X9" s="10">
         <v>1009</v>
       </c>
-      <c r="Y9" s="8">
-        <v>3</v>
+      <c r="Y9" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="Z9" s="10">
         <v>10021</v>
@@ -1993,8 +1996,8 @@
       <c r="X10" s="10">
         <v>1009</v>
       </c>
-      <c r="Y10" s="8">
-        <v>3</v>
+      <c r="Y10" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="Z10" s="10">
         <v>10021</v>
@@ -2038,7 +2041,7 @@
         <v>45</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H11" s="4">
         <v>1010</v>
@@ -2091,8 +2094,8 @@
       <c r="X11" s="10">
         <v>1009</v>
       </c>
-      <c r="Y11" s="8">
-        <v>3</v>
+      <c r="Y11" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="Z11" s="10">
         <v>10021</v>
@@ -2136,7 +2139,7 @@
         <v>45</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H12" s="4">
         <v>1010</v>
@@ -2189,8 +2192,8 @@
       <c r="X12" s="10">
         <v>1009</v>
       </c>
-      <c r="Y12" s="8">
-        <v>3</v>
+      <c r="Y12" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="Z12" s="10">
         <v>10021</v>
@@ -2225,16 +2228,16 @@
         <v>42</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>45</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H13" s="4">
         <v>1010</v>
@@ -2287,8 +2290,8 @@
       <c r="X13" s="10">
         <v>1009</v>
       </c>
-      <c r="Y13" s="8">
-        <v>3</v>
+      <c r="Y13" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="Z13" s="10">
         <v>10021</v>
@@ -2323,16 +2326,16 @@
         <v>42</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>45</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H14" s="4">
         <v>1010</v>
@@ -2385,8 +2388,8 @@
       <c r="X14" s="10">
         <v>1009</v>
       </c>
-      <c r="Y14" s="8">
-        <v>3</v>
+      <c r="Y14" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="Z14" s="10">
         <v>10021</v>
@@ -2421,16 +2424,16 @@
         <v>42</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>45</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H15" s="4">
         <v>1010</v>
@@ -2483,8 +2486,8 @@
       <c r="X15" s="10">
         <v>1009</v>
       </c>
-      <c r="Y15" s="8">
-        <v>3</v>
+      <c r="Y15" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="Z15" s="10">
         <v>10021</v>
@@ -2519,16 +2522,16 @@
         <v>42</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>45</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H16" s="4">
         <v>1010</v>
@@ -2581,8 +2584,8 @@
       <c r="X16" s="10">
         <v>1009</v>
       </c>
-      <c r="Y16" s="8">
-        <v>3</v>
+      <c r="Y16" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="Z16" s="10">
         <v>10021</v>
@@ -2617,16 +2620,16 @@
         <v>42</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>45</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H17" s="4">
         <v>1010</v>
@@ -2679,8 +2682,8 @@
       <c r="X17" s="10">
         <v>1009</v>
       </c>
-      <c r="Y17" s="8">
-        <v>3</v>
+      <c r="Y17" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="Z17" s="10">
         <v>10021</v>

--- a/Packages/cn.etetet.wow/Luban/Datas/Unit.xlsx
+++ b/Packages/cn.etetet.wow/Luban/Datas/Unit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanghai/Documents/WOW/Packages/cn.etetet.wow/Luban/Datas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2FDAE1-7054-5C48-B972-1CCD0C4D8EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99876536-66FE-0F46-9375-7A65C57400E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4200" yWindow="4160" windowWidth="32220" windowHeight="15760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="66">
   <si>
     <t>##var</t>
   </si>
@@ -219,6 +219,22 @@
   </si>
   <si>
     <t>Player</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapName</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>所在地图</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -602,40 +618,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG17"/>
+  <dimension ref="A1:AH17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.5" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
     <col min="3" max="3" width="13.33203125" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" customWidth="1"/>
-    <col min="5" max="5" width="9.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" customWidth="1"/>
-    <col min="8" max="8" width="6.6640625" customWidth="1"/>
-    <col min="9" max="9" width="6.1640625" customWidth="1"/>
-    <col min="10" max="10" width="5.1640625" customWidth="1"/>
-    <col min="11" max="11" width="6.1640625" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" customWidth="1"/>
-    <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="6.1640625" customWidth="1"/>
-    <col min="15" max="15" width="5.1640625" customWidth="1"/>
-    <col min="16" max="16" width="6.1640625" customWidth="1"/>
-    <col min="17" max="17" width="5.1640625" customWidth="1"/>
-    <col min="18" max="18" width="6.1640625" customWidth="1"/>
-    <col min="19" max="19" width="7.1640625" customWidth="1"/>
-    <col min="20" max="20" width="6.1640625" customWidth="1"/>
-    <col min="21" max="21" width="5.1640625" customWidth="1"/>
-    <col min="22" max="23" width="6.1640625" customWidth="1"/>
-    <col min="24" max="24" width="5.1640625" customWidth="1"/>
-    <col min="25" max="25" width="7.1640625" customWidth="1"/>
-    <col min="26" max="26" width="6.1640625" customWidth="1"/>
-    <col min="27" max="29" width="5.1640625" customWidth="1"/>
-    <col min="30" max="30" width="6.1640625" customWidth="1"/>
-    <col min="31" max="33" width="5.1640625" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" customWidth="1"/>
+    <col min="6" max="6" width="9.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.6640625" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" customWidth="1"/>
+    <col min="9" max="9" width="6.6640625" customWidth="1"/>
+    <col min="10" max="10" width="6.1640625" customWidth="1"/>
+    <col min="11" max="11" width="5.1640625" customWidth="1"/>
+    <col min="12" max="12" width="6.1640625" customWidth="1"/>
+    <col min="13" max="13" width="5.1640625" customWidth="1"/>
+    <col min="14" max="14" width="8" customWidth="1"/>
+    <col min="15" max="15" width="6.1640625" customWidth="1"/>
+    <col min="16" max="16" width="5.1640625" customWidth="1"/>
+    <col min="17" max="17" width="6.1640625" customWidth="1"/>
+    <col min="18" max="18" width="5.1640625" customWidth="1"/>
+    <col min="19" max="19" width="6.1640625" customWidth="1"/>
+    <col min="20" max="20" width="7.1640625" customWidth="1"/>
+    <col min="21" max="21" width="6.1640625" customWidth="1"/>
+    <col min="22" max="22" width="5.1640625" customWidth="1"/>
+    <col min="23" max="24" width="6.1640625" customWidth="1"/>
+    <col min="25" max="25" width="5.1640625" customWidth="1"/>
+    <col min="26" max="26" width="7.1640625" customWidth="1"/>
+    <col min="27" max="27" width="6.1640625" customWidth="1"/>
+    <col min="28" max="30" width="5.1640625" customWidth="1"/>
+    <col min="31" max="31" width="6.1640625" customWidth="1"/>
+    <col min="32" max="34" width="5.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:34">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -648,17 +665,19 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="8"/>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
@@ -683,8 +702,9 @@
       <c r="AE1" s="8"/>
       <c r="AF1" s="8"/>
       <c r="AG1" s="8"/>
+      <c r="AH1" s="8"/>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:34">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -697,17 +717,19 @@
       <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="8"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
@@ -732,8 +754,9 @@
       <c r="AE2" s="8"/>
       <c r="AF2" s="8"/>
       <c r="AG2" s="8"/>
+      <c r="AH2" s="8"/>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" spans="1:34">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -741,14 +764,14 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="1"/>
+      <c r="G3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="1"/>
+      <c r="I3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
@@ -773,8 +796,9 @@
       <c r="AE3" s="8"/>
       <c r="AF3" s="8"/>
       <c r="AG3" s="8"/>
+      <c r="AH3" s="8"/>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:34">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -788,68 +812,71 @@
         <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="I4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="9"/>
+      <c r="K4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="10"/>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="10"/>
+      <c r="M4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="10" t="s">
+      <c r="N4" s="9"/>
+      <c r="O4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="O4" s="10"/>
-      <c r="P4" s="9" t="s">
+      <c r="P4" s="10"/>
+      <c r="Q4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="10" t="s">
+      <c r="R4" s="9"/>
+      <c r="S4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="S4" s="11"/>
-      <c r="T4" s="9" t="s">
+      <c r="T4" s="11"/>
+      <c r="U4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="U4" s="12"/>
-      <c r="V4" s="10" t="s">
+      <c r="V4" s="12"/>
+      <c r="W4" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="W4" s="11"/>
-      <c r="X4" s="9" t="s">
+      <c r="X4" s="11"/>
+      <c r="Y4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="Y4" s="12"/>
-      <c r="Z4" s="10" t="s">
+      <c r="Z4" s="12"/>
+      <c r="AA4" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="AA4" s="11"/>
-      <c r="AB4" s="9" t="s">
+      <c r="AB4" s="11"/>
+      <c r="AC4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="AC4" s="12"/>
-      <c r="AD4" s="10" t="s">
+      <c r="AD4" s="12"/>
+      <c r="AE4" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="AE4" s="11"/>
-      <c r="AF4" s="9" t="s">
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="AG4" s="12"/>
+      <c r="AH4" s="12"/>
     </row>
-    <row r="5" spans="1:33">
+    <row r="5" spans="1:34">
       <c r="B5" s="2">
         <v>1001</v>
       </c>
@@ -859,95 +886,96 @@
       <c r="D5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2"/>
+      <c r="F5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <v>1010</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="K5" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="5">
+      <c r="L5" s="5">
         <v>29000</v>
       </c>
-      <c r="L5" s="6">
+      <c r="M5" s="6">
         <v>1012</v>
       </c>
-      <c r="M5" s="5">
+      <c r="N5" s="5">
         <v>-136000</v>
       </c>
-      <c r="N5" s="6">
+      <c r="O5" s="6">
         <v>10001</v>
       </c>
-      <c r="O5" s="5">
+      <c r="P5" s="5">
         <v>6000</v>
       </c>
-      <c r="P5" s="7">
+      <c r="Q5" s="7">
         <v>10051</v>
       </c>
-      <c r="Q5" s="5">
+      <c r="R5" s="5">
         <v>500</v>
       </c>
-      <c r="R5" s="6">
+      <c r="S5" s="6">
         <v>10061</v>
       </c>
-      <c r="S5" s="5">
+      <c r="T5" s="5">
         <v>100000</v>
       </c>
-      <c r="T5" s="7">
+      <c r="U5" s="7">
         <v>10071</v>
       </c>
-      <c r="U5" s="5">
+      <c r="V5" s="5">
         <v>1780</v>
       </c>
-      <c r="V5" s="7">
+      <c r="W5" s="7">
         <v>10081</v>
       </c>
-      <c r="W5" s="5">
+      <c r="X5" s="5">
         <v>68000</v>
       </c>
-      <c r="X5" s="7">
+      <c r="Y5" s="7">
         <v>1009</v>
       </c>
-      <c r="Y5" s="5" t="s">
+      <c r="Z5" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="Z5" s="7">
+      <c r="AA5" s="7">
         <v>10021</v>
       </c>
-      <c r="AA5" s="5">
+      <c r="AB5" s="5">
         <v>1000</v>
       </c>
-      <c r="AB5" s="7">
+      <c r="AC5" s="7">
         <v>1001</v>
       </c>
-      <c r="AC5" s="5">
+      <c r="AD5" s="5">
         <v>1000</v>
       </c>
-      <c r="AD5" s="7">
+      <c r="AE5" s="7">
         <v>10041</v>
       </c>
-      <c r="AE5" s="5">
+      <c r="AF5" s="5">
         <v>1000</v>
       </c>
-      <c r="AF5" s="7">
+      <c r="AG5" s="7">
         <v>1003</v>
       </c>
-      <c r="AG5" s="5">
+      <c r="AH5" s="5">
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:34">
       <c r="B6" s="2">
         <v>1002</v>
       </c>
@@ -957,95 +985,98 @@
       <c r="D6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <v>1010</v>
       </c>
-      <c r="I6" s="5">
+      <c r="J6" s="5">
         <v>56000</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="K6" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="5">
+      <c r="L6" s="5">
         <v>30000</v>
       </c>
-      <c r="L6" s="6">
+      <c r="M6" s="6">
         <v>1012</v>
       </c>
-      <c r="M6" s="5">
+      <c r="N6" s="5">
         <v>-138000</v>
       </c>
-      <c r="N6" s="6">
+      <c r="O6" s="6">
         <v>10001</v>
       </c>
-      <c r="O6" s="5">
+      <c r="P6" s="5">
         <v>0</v>
       </c>
-      <c r="P6" s="7">
+      <c r="Q6" s="7">
         <v>10051</v>
       </c>
-      <c r="Q6" s="5">
+      <c r="R6" s="5">
         <v>500</v>
       </c>
-      <c r="R6" s="6">
+      <c r="S6" s="6">
         <v>10061</v>
       </c>
-      <c r="S6" s="5">
+      <c r="T6" s="5">
         <v>0</v>
       </c>
-      <c r="T6" s="7">
+      <c r="U6" s="7">
         <v>10071</v>
       </c>
-      <c r="U6" s="5">
+      <c r="V6" s="5">
         <v>500</v>
       </c>
-      <c r="V6" s="7">
+      <c r="W6" s="7">
         <v>10081</v>
       </c>
-      <c r="W6" s="5">
+      <c r="X6" s="5">
         <v>30000</v>
       </c>
-      <c r="X6" s="7">
+      <c r="Y6" s="7">
         <v>1009</v>
       </c>
-      <c r="Y6" s="5" t="s">
+      <c r="Z6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="Z6" s="7">
+      <c r="AA6" s="7">
         <v>10021</v>
       </c>
-      <c r="AA6" s="5">
-        <v>100</v>
-      </c>
-      <c r="AB6" s="7">
+      <c r="AB6" s="5">
+        <v>100</v>
+      </c>
+      <c r="AC6" s="7">
         <v>1001</v>
       </c>
-      <c r="AC6" s="5">
-        <v>100</v>
-      </c>
-      <c r="AD6" s="7">
+      <c r="AD6" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE6" s="7">
         <v>10041</v>
       </c>
-      <c r="AE6" s="5">
-        <v>100</v>
-      </c>
-      <c r="AF6" s="7">
+      <c r="AF6" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG6" s="7">
         <v>1003</v>
       </c>
-      <c r="AG6" s="5">
+      <c r="AH6" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:33">
+    <row r="7" spans="1:34">
       <c r="B7" s="2">
         <v>1003</v>
       </c>
@@ -1055,95 +1086,98 @@
       <c r="D7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>1010</v>
       </c>
-      <c r="I7" s="5">
+      <c r="J7" s="5">
         <v>58740</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="K7" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K7" s="5">
+      <c r="L7" s="5">
         <v>29090</v>
       </c>
-      <c r="L7" s="6">
+      <c r="M7" s="6">
         <v>1012</v>
       </c>
-      <c r="M7" s="5">
+      <c r="N7" s="5">
         <v>-148001</v>
       </c>
-      <c r="N7" s="6">
+      <c r="O7" s="6">
         <v>10001</v>
       </c>
-      <c r="O7" s="5">
+      <c r="P7" s="5">
         <v>0</v>
       </c>
-      <c r="P7" s="7">
+      <c r="Q7" s="7">
         <v>10051</v>
       </c>
-      <c r="Q7" s="5">
+      <c r="R7" s="5">
         <v>500</v>
       </c>
-      <c r="R7" s="6">
+      <c r="S7" s="6">
         <v>10061</v>
       </c>
-      <c r="S7" s="5">
+      <c r="T7" s="5">
         <v>0</v>
       </c>
-      <c r="T7" s="7">
+      <c r="U7" s="7">
         <v>10071</v>
       </c>
-      <c r="U7" s="5">
+      <c r="V7" s="5">
         <v>500</v>
       </c>
-      <c r="V7" s="7">
+      <c r="W7" s="7">
         <v>10081</v>
       </c>
-      <c r="W7" s="5">
+      <c r="X7" s="5">
         <v>30000</v>
       </c>
-      <c r="X7" s="7">
+      <c r="Y7" s="7">
         <v>1009</v>
       </c>
-      <c r="Y7" s="5" t="s">
+      <c r="Z7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="Z7" s="7">
+      <c r="AA7" s="7">
         <v>10021</v>
       </c>
-      <c r="AA7" s="5">
-        <v>100</v>
-      </c>
-      <c r="AB7" s="7">
+      <c r="AB7" s="5">
+        <v>100</v>
+      </c>
+      <c r="AC7" s="7">
         <v>1001</v>
       </c>
-      <c r="AC7" s="5">
-        <v>100</v>
-      </c>
-      <c r="AD7" s="7">
+      <c r="AD7" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE7" s="7">
         <v>10041</v>
       </c>
-      <c r="AE7" s="5">
-        <v>100</v>
-      </c>
-      <c r="AF7" s="7">
+      <c r="AF7" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG7" s="7">
         <v>1003</v>
       </c>
-      <c r="AG7" s="5">
+      <c r="AH7" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:33">
+    <row r="8" spans="1:34">
       <c r="B8" s="2">
         <v>1004</v>
       </c>
@@ -1153,95 +1187,98 @@
       <c r="D8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="2">
+      <c r="I8" s="2">
         <v>1010</v>
       </c>
-      <c r="I8" s="5">
+      <c r="J8" s="5">
         <v>21600</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="K8" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K8" s="5">
+      <c r="L8" s="5">
         <v>26800</v>
       </c>
-      <c r="L8" s="6">
+      <c r="M8" s="6">
         <v>1012</v>
       </c>
-      <c r="M8" s="5">
+      <c r="N8" s="5">
         <v>-58702</v>
       </c>
-      <c r="N8" s="6">
+      <c r="O8" s="6">
         <v>10001</v>
       </c>
-      <c r="O8" s="5">
+      <c r="P8" s="5">
         <v>2000</v>
       </c>
-      <c r="P8" s="7">
+      <c r="Q8" s="7">
         <v>10051</v>
       </c>
-      <c r="Q8" s="5">
+      <c r="R8" s="5">
         <v>500</v>
       </c>
-      <c r="R8" s="6">
+      <c r="S8" s="6">
         <v>10061</v>
       </c>
-      <c r="S8" s="5">
+      <c r="T8" s="5">
         <v>10000</v>
       </c>
-      <c r="T8" s="7">
+      <c r="U8" s="7">
         <v>10071</v>
       </c>
-      <c r="U8" s="5">
+      <c r="V8" s="5">
         <v>500</v>
       </c>
-      <c r="V8" s="7">
+      <c r="W8" s="7">
         <v>10081</v>
       </c>
-      <c r="W8" s="5">
+      <c r="X8" s="5">
         <v>30000</v>
       </c>
-      <c r="X8" s="7">
+      <c r="Y8" s="7">
         <v>1009</v>
       </c>
-      <c r="Y8" s="5" t="s">
+      <c r="Z8" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="Z8" s="7">
+      <c r="AA8" s="7">
         <v>10021</v>
       </c>
-      <c r="AA8" s="5">
-        <v>100</v>
-      </c>
-      <c r="AB8" s="7">
+      <c r="AB8" s="5">
+        <v>100</v>
+      </c>
+      <c r="AC8" s="7">
         <v>1001</v>
       </c>
-      <c r="AC8" s="5">
-        <v>100</v>
-      </c>
-      <c r="AD8" s="7">
+      <c r="AD8" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE8" s="7">
         <v>10041</v>
       </c>
-      <c r="AE8" s="5">
-        <v>100</v>
-      </c>
-      <c r="AF8" s="7">
+      <c r="AF8" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG8" s="7">
         <v>1003</v>
       </c>
-      <c r="AG8" s="5">
+      <c r="AH8" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" spans="1:34">
       <c r="B9" s="2">
         <v>1005</v>
       </c>
@@ -1251,95 +1288,98 @@
       <c r="D9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H9" s="2">
+      <c r="I9" s="2">
         <v>1010</v>
       </c>
-      <c r="I9" s="5">
+      <c r="J9" s="5">
         <v>56000</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="K9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K9" s="5">
+      <c r="L9" s="5">
         <v>25180</v>
       </c>
-      <c r="L9" s="6">
+      <c r="M9" s="6">
         <v>1012</v>
       </c>
-      <c r="M9" s="5">
+      <c r="N9" s="5">
         <v>-23633</v>
       </c>
-      <c r="N9" s="6">
+      <c r="O9" s="6">
         <v>10001</v>
       </c>
-      <c r="O9" s="5">
+      <c r="P9" s="5">
         <v>2000</v>
       </c>
-      <c r="P9" s="7">
+      <c r="Q9" s="7">
         <v>10051</v>
       </c>
-      <c r="Q9" s="5">
+      <c r="R9" s="5">
         <v>500</v>
       </c>
-      <c r="R9" s="6">
+      <c r="S9" s="6">
         <v>10061</v>
       </c>
-      <c r="S9" s="5">
+      <c r="T9" s="5">
         <v>10000</v>
       </c>
-      <c r="T9" s="7">
+      <c r="U9" s="7">
         <v>10071</v>
       </c>
-      <c r="U9" s="5">
+      <c r="V9" s="5">
         <v>500</v>
       </c>
-      <c r="V9" s="7">
+      <c r="W9" s="7">
         <v>10081</v>
       </c>
-      <c r="W9" s="5">
+      <c r="X9" s="5">
         <v>30000</v>
       </c>
-      <c r="X9" s="7">
+      <c r="Y9" s="7">
         <v>1009</v>
       </c>
-      <c r="Y9" s="5" t="s">
+      <c r="Z9" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="Z9" s="7">
+      <c r="AA9" s="7">
         <v>10021</v>
       </c>
-      <c r="AA9" s="5">
-        <v>100</v>
-      </c>
-      <c r="AB9" s="7">
+      <c r="AB9" s="5">
+        <v>100</v>
+      </c>
+      <c r="AC9" s="7">
         <v>1001</v>
       </c>
-      <c r="AC9" s="5">
-        <v>100</v>
-      </c>
-      <c r="AD9" s="7">
+      <c r="AD9" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE9" s="7">
         <v>10041</v>
       </c>
-      <c r="AE9" s="5">
-        <v>100</v>
-      </c>
-      <c r="AF9" s="7">
+      <c r="AF9" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG9" s="7">
         <v>1003</v>
       </c>
-      <c r="AG9" s="5">
+      <c r="AH9" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:33">
+    <row r="10" spans="1:34">
       <c r="B10" s="2">
         <v>1006</v>
       </c>
@@ -1349,95 +1389,98 @@
       <c r="D10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H10" s="2">
+      <c r="I10" s="2">
         <v>1010</v>
       </c>
-      <c r="I10" s="5">
+      <c r="J10" s="5">
         <v>36310</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="K10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K10" s="5">
+      <c r="L10" s="5">
         <v>25180</v>
       </c>
-      <c r="L10" s="6">
+      <c r="M10" s="6">
         <v>1012</v>
       </c>
-      <c r="M10" s="5">
+      <c r="N10" s="5">
         <v>-23634</v>
       </c>
-      <c r="N10" s="6">
+      <c r="O10" s="6">
         <v>10001</v>
       </c>
-      <c r="O10" s="5">
+      <c r="P10" s="5">
         <v>2000</v>
       </c>
-      <c r="P10" s="7">
+      <c r="Q10" s="7">
         <v>10051</v>
       </c>
-      <c r="Q10" s="5">
+      <c r="R10" s="5">
         <v>500</v>
       </c>
-      <c r="R10" s="6">
+      <c r="S10" s="6">
         <v>10061</v>
       </c>
-      <c r="S10" s="5">
+      <c r="T10" s="5">
         <v>10000</v>
       </c>
-      <c r="T10" s="7">
+      <c r="U10" s="7">
         <v>10071</v>
       </c>
-      <c r="U10" s="5">
+      <c r="V10" s="5">
         <v>500</v>
       </c>
-      <c r="V10" s="7">
+      <c r="W10" s="7">
         <v>10081</v>
       </c>
-      <c r="W10" s="5">
+      <c r="X10" s="5">
         <v>30000</v>
       </c>
-      <c r="X10" s="7">
+      <c r="Y10" s="7">
         <v>1009</v>
       </c>
-      <c r="Y10" s="5" t="s">
+      <c r="Z10" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="Z10" s="7">
+      <c r="AA10" s="7">
         <v>10021</v>
       </c>
-      <c r="AA10" s="5">
-        <v>100</v>
-      </c>
-      <c r="AB10" s="7">
+      <c r="AB10" s="5">
+        <v>100</v>
+      </c>
+      <c r="AC10" s="7">
         <v>1001</v>
       </c>
-      <c r="AC10" s="5">
-        <v>100</v>
-      </c>
-      <c r="AD10" s="7">
+      <c r="AD10" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE10" s="7">
         <v>10041</v>
       </c>
-      <c r="AE10" s="5">
-        <v>100</v>
-      </c>
-      <c r="AF10" s="7">
+      <c r="AF10" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG10" s="7">
         <v>1003</v>
       </c>
-      <c r="AG10" s="5">
+      <c r="AH10" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:33">
+    <row r="11" spans="1:34">
       <c r="B11" s="2">
         <v>1007</v>
       </c>
@@ -1447,95 +1490,98 @@
       <c r="D11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H11" s="2">
+      <c r="I11" s="2">
         <v>1010</v>
       </c>
-      <c r="I11" s="5">
+      <c r="J11" s="5">
         <v>67170</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="K11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K11" s="5">
+      <c r="L11" s="5">
         <v>25180</v>
       </c>
-      <c r="L11" s="6">
+      <c r="M11" s="6">
         <v>1012</v>
       </c>
-      <c r="M11" s="5">
+      <c r="N11" s="5">
         <v>-40495</v>
       </c>
-      <c r="N11" s="6">
+      <c r="O11" s="6">
         <v>10001</v>
       </c>
-      <c r="O11" s="5">
+      <c r="P11" s="5">
         <v>2000</v>
       </c>
-      <c r="P11" s="7">
+      <c r="Q11" s="7">
         <v>10051</v>
       </c>
-      <c r="Q11" s="5">
+      <c r="R11" s="5">
         <v>500</v>
       </c>
-      <c r="R11" s="6">
+      <c r="S11" s="6">
         <v>10061</v>
       </c>
-      <c r="S11" s="5">
+      <c r="T11" s="5">
         <v>10000</v>
       </c>
-      <c r="T11" s="7">
+      <c r="U11" s="7">
         <v>10071</v>
       </c>
-      <c r="U11" s="5">
+      <c r="V11" s="5">
         <v>500</v>
       </c>
-      <c r="V11" s="7">
+      <c r="W11" s="7">
         <v>10081</v>
       </c>
-      <c r="W11" s="5">
+      <c r="X11" s="5">
         <v>30000</v>
       </c>
-      <c r="X11" s="7">
+      <c r="Y11" s="7">
         <v>1009</v>
       </c>
-      <c r="Y11" s="5" t="s">
+      <c r="Z11" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="Z11" s="7">
+      <c r="AA11" s="7">
         <v>10021</v>
       </c>
-      <c r="AA11" s="5">
-        <v>100</v>
-      </c>
-      <c r="AB11" s="7">
+      <c r="AB11" s="5">
+        <v>100</v>
+      </c>
+      <c r="AC11" s="7">
         <v>1001</v>
       </c>
-      <c r="AC11" s="5">
-        <v>100</v>
-      </c>
-      <c r="AD11" s="7">
+      <c r="AD11" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE11" s="7">
         <v>10041</v>
       </c>
-      <c r="AE11" s="5">
-        <v>100</v>
-      </c>
-      <c r="AF11" s="7">
+      <c r="AF11" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG11" s="7">
         <v>1003</v>
       </c>
-      <c r="AG11" s="5">
+      <c r="AH11" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:33">
+    <row r="12" spans="1:34">
       <c r="B12" s="2">
         <v>1008</v>
       </c>
@@ -1545,95 +1591,98 @@
       <c r="D12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="H12" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="2">
+      <c r="I12" s="2">
         <v>1010</v>
       </c>
-      <c r="I12" s="5">
+      <c r="J12" s="5">
         <v>59600</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="K12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K12" s="5">
+      <c r="L12" s="5">
         <v>25800</v>
       </c>
-      <c r="L12" s="6">
+      <c r="M12" s="6">
         <v>1012</v>
       </c>
-      <c r="M12" s="5">
+      <c r="N12" s="5">
         <v>-87866</v>
       </c>
-      <c r="N12" s="6">
+      <c r="O12" s="6">
         <v>10001</v>
       </c>
-      <c r="O12" s="5">
+      <c r="P12" s="5">
         <v>2000</v>
       </c>
-      <c r="P12" s="7">
+      <c r="Q12" s="7">
         <v>10051</v>
       </c>
-      <c r="Q12" s="5">
+      <c r="R12" s="5">
         <v>500</v>
       </c>
-      <c r="R12" s="6">
+      <c r="S12" s="6">
         <v>10061</v>
       </c>
-      <c r="S12" s="5">
+      <c r="T12" s="5">
         <v>10000</v>
       </c>
-      <c r="T12" s="7">
+      <c r="U12" s="7">
         <v>10071</v>
       </c>
-      <c r="U12" s="5">
+      <c r="V12" s="5">
         <v>500</v>
       </c>
-      <c r="V12" s="7">
+      <c r="W12" s="7">
         <v>10081</v>
       </c>
-      <c r="W12" s="5">
+      <c r="X12" s="5">
         <v>30000</v>
       </c>
-      <c r="X12" s="7">
+      <c r="Y12" s="7">
         <v>1009</v>
       </c>
-      <c r="Y12" s="5" t="s">
+      <c r="Z12" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="Z12" s="7">
+      <c r="AA12" s="7">
         <v>10021</v>
       </c>
-      <c r="AA12" s="5">
-        <v>100</v>
-      </c>
-      <c r="AB12" s="7">
+      <c r="AB12" s="5">
+        <v>100</v>
+      </c>
+      <c r="AC12" s="7">
         <v>1001</v>
       </c>
-      <c r="AC12" s="5">
-        <v>100</v>
-      </c>
-      <c r="AD12" s="7">
+      <c r="AD12" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE12" s="7">
         <v>10041</v>
       </c>
-      <c r="AE12" s="5">
-        <v>100</v>
-      </c>
-      <c r="AF12" s="7">
+      <c r="AF12" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG12" s="7">
         <v>1003</v>
       </c>
-      <c r="AG12" s="5">
+      <c r="AH12" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:33">
+    <row r="13" spans="1:34">
       <c r="B13" s="2">
         <v>1009</v>
       </c>
@@ -1643,95 +1692,98 @@
       <c r="D13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="H13" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="H13" s="2">
+      <c r="I13" s="2">
         <v>1010</v>
       </c>
-      <c r="I13" s="5">
+      <c r="J13" s="5">
         <v>58740</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="K13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K13" s="5">
+      <c r="L13" s="5">
         <v>28100</v>
       </c>
-      <c r="L13" s="6">
+      <c r="M13" s="6">
         <v>1012</v>
       </c>
-      <c r="M13" s="5">
+      <c r="N13" s="5">
         <v>-141407</v>
       </c>
-      <c r="N13" s="6">
+      <c r="O13" s="6">
         <v>10001</v>
       </c>
-      <c r="O13" s="5">
+      <c r="P13" s="5">
         <v>2000</v>
       </c>
-      <c r="P13" s="7">
+      <c r="Q13" s="7">
         <v>10051</v>
       </c>
-      <c r="Q13" s="5">
+      <c r="R13" s="5">
         <v>2000</v>
       </c>
-      <c r="R13" s="6">
+      <c r="S13" s="6">
         <v>10061</v>
       </c>
-      <c r="S13" s="5">
+      <c r="T13" s="5">
         <v>10000</v>
       </c>
-      <c r="T13" s="7">
+      <c r="U13" s="7">
         <v>10071</v>
       </c>
-      <c r="U13" s="5">
+      <c r="V13" s="5">
         <v>500</v>
       </c>
-      <c r="V13" s="7">
+      <c r="W13" s="7">
         <v>10081</v>
       </c>
-      <c r="W13" s="5">
+      <c r="X13" s="5">
         <v>30000</v>
       </c>
-      <c r="X13" s="7">
+      <c r="Y13" s="7">
         <v>1009</v>
       </c>
-      <c r="Y13" s="5" t="s">
+      <c r="Z13" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="Z13" s="7">
+      <c r="AA13" s="7">
         <v>10021</v>
       </c>
-      <c r="AA13" s="5">
-        <v>100</v>
-      </c>
-      <c r="AB13" s="7">
+      <c r="AB13" s="5">
+        <v>100</v>
+      </c>
+      <c r="AC13" s="7">
         <v>1001</v>
       </c>
-      <c r="AC13" s="5">
-        <v>100</v>
-      </c>
-      <c r="AD13" s="7">
+      <c r="AD13" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE13" s="7">
         <v>10041</v>
       </c>
-      <c r="AE13" s="5">
-        <v>100</v>
-      </c>
-      <c r="AF13" s="7">
+      <c r="AF13" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG13" s="7">
         <v>1003</v>
       </c>
-      <c r="AG13" s="5">
+      <c r="AH13" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:33">
+    <row r="14" spans="1:34">
       <c r="B14" s="2">
         <v>1010</v>
       </c>
@@ -1741,95 +1793,98 @@
       <c r="D14" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="H14" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H14" s="2">
+      <c r="I14" s="2">
         <v>1010</v>
       </c>
-      <c r="I14" s="5">
+      <c r="J14" s="5">
         <v>58740</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="K14" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K14" s="5">
+      <c r="L14" s="5">
         <v>28100</v>
       </c>
-      <c r="L14" s="6">
+      <c r="M14" s="6">
         <v>1012</v>
       </c>
-      <c r="M14" s="5">
+      <c r="N14" s="5">
         <v>-130408</v>
       </c>
-      <c r="N14" s="6">
+      <c r="O14" s="6">
         <v>10001</v>
       </c>
-      <c r="O14" s="5">
+      <c r="P14" s="5">
         <v>2000</v>
       </c>
-      <c r="P14" s="7">
+      <c r="Q14" s="7">
         <v>10051</v>
       </c>
-      <c r="Q14" s="5">
+      <c r="R14" s="5">
         <v>2000</v>
       </c>
-      <c r="R14" s="6">
+      <c r="S14" s="6">
         <v>10061</v>
       </c>
-      <c r="S14" s="5">
+      <c r="T14" s="5">
         <v>10000</v>
       </c>
-      <c r="T14" s="7">
+      <c r="U14" s="7">
         <v>10071</v>
       </c>
-      <c r="U14" s="5">
+      <c r="V14" s="5">
         <v>500</v>
       </c>
-      <c r="V14" s="7">
+      <c r="W14" s="7">
         <v>10081</v>
       </c>
-      <c r="W14" s="5">
+      <c r="X14" s="5">
         <v>30000</v>
       </c>
-      <c r="X14" s="7">
+      <c r="Y14" s="7">
         <v>1009</v>
       </c>
-      <c r="Y14" s="5" t="s">
+      <c r="Z14" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="Z14" s="7">
+      <c r="AA14" s="7">
         <v>10021</v>
       </c>
-      <c r="AA14" s="5">
-        <v>100</v>
-      </c>
-      <c r="AB14" s="7">
+      <c r="AB14" s="5">
+        <v>100</v>
+      </c>
+      <c r="AC14" s="7">
         <v>1001</v>
       </c>
-      <c r="AC14" s="5">
-        <v>100</v>
-      </c>
-      <c r="AD14" s="7">
+      <c r="AD14" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE14" s="7">
         <v>10041</v>
       </c>
-      <c r="AE14" s="5">
-        <v>100</v>
-      </c>
-      <c r="AF14" s="7">
+      <c r="AF14" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG14" s="7">
         <v>1003</v>
       </c>
-      <c r="AG14" s="5">
+      <c r="AH14" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:33">
+    <row r="15" spans="1:34">
       <c r="B15" s="2">
         <v>1011</v>
       </c>
@@ -1839,95 +1894,98 @@
       <c r="D15" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="H15" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="H15" s="2">
+      <c r="I15" s="2">
         <v>1010</v>
       </c>
-      <c r="I15" s="5">
+      <c r="J15" s="5">
         <v>67480</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="K15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K15" s="5">
+      <c r="L15" s="5">
         <v>28850</v>
       </c>
-      <c r="L15" s="6">
+      <c r="M15" s="6">
         <v>1012</v>
       </c>
-      <c r="M15" s="5">
+      <c r="N15" s="5">
         <v>-130409</v>
       </c>
-      <c r="N15" s="6">
+      <c r="O15" s="6">
         <v>10001</v>
       </c>
-      <c r="O15" s="5">
+      <c r="P15" s="5">
         <v>2000</v>
       </c>
-      <c r="P15" s="7">
+      <c r="Q15" s="7">
         <v>10051</v>
       </c>
-      <c r="Q15" s="5">
+      <c r="R15" s="5">
         <v>2000</v>
       </c>
-      <c r="R15" s="6">
+      <c r="S15" s="6">
         <v>10061</v>
       </c>
-      <c r="S15" s="5">
+      <c r="T15" s="5">
         <v>10000</v>
       </c>
-      <c r="T15" s="7">
+      <c r="U15" s="7">
         <v>10071</v>
       </c>
-      <c r="U15" s="5">
+      <c r="V15" s="5">
         <v>500</v>
       </c>
-      <c r="V15" s="7">
+      <c r="W15" s="7">
         <v>10081</v>
       </c>
-      <c r="W15" s="5">
+      <c r="X15" s="5">
         <v>30000</v>
       </c>
-      <c r="X15" s="7">
+      <c r="Y15" s="7">
         <v>1009</v>
       </c>
-      <c r="Y15" s="5" t="s">
+      <c r="Z15" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="Z15" s="7">
+      <c r="AA15" s="7">
         <v>10021</v>
       </c>
-      <c r="AA15" s="5">
-        <v>100</v>
-      </c>
-      <c r="AB15" s="7">
+      <c r="AB15" s="5">
+        <v>100</v>
+      </c>
+      <c r="AC15" s="7">
         <v>1001</v>
       </c>
-      <c r="AC15" s="5">
-        <v>100</v>
-      </c>
-      <c r="AD15" s="7">
+      <c r="AD15" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE15" s="7">
         <v>10041</v>
       </c>
-      <c r="AE15" s="5">
-        <v>100</v>
-      </c>
-      <c r="AF15" s="7">
+      <c r="AF15" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG15" s="7">
         <v>1003</v>
       </c>
-      <c r="AG15" s="5">
+      <c r="AH15" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:33">
+    <row r="16" spans="1:34">
       <c r="B16" s="2">
         <v>1012</v>
       </c>
@@ -1937,95 +1995,98 @@
       <c r="D16" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="H16" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H16" s="2">
+      <c r="I16" s="2">
         <v>1010</v>
       </c>
-      <c r="I16" s="5">
+      <c r="J16" s="5">
         <v>67480</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="K16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K16" s="5">
+      <c r="L16" s="5">
         <v>27510</v>
       </c>
-      <c r="L16" s="6">
+      <c r="M16" s="6">
         <v>1012</v>
       </c>
-      <c r="M16" s="5">
+      <c r="N16" s="5">
         <v>-34791</v>
       </c>
-      <c r="N16" s="6">
+      <c r="O16" s="6">
         <v>10001</v>
       </c>
-      <c r="O16" s="5">
+      <c r="P16" s="5">
         <v>2000</v>
       </c>
-      <c r="P16" s="7">
+      <c r="Q16" s="7">
         <v>10051</v>
       </c>
-      <c r="Q16" s="5">
+      <c r="R16" s="5">
         <v>2000</v>
       </c>
-      <c r="R16" s="6">
+      <c r="S16" s="6">
         <v>10061</v>
       </c>
-      <c r="S16" s="5">
+      <c r="T16" s="5">
         <v>10000</v>
       </c>
-      <c r="T16" s="7">
+      <c r="U16" s="7">
         <v>10071</v>
       </c>
-      <c r="U16" s="5">
+      <c r="V16" s="5">
         <v>500</v>
       </c>
-      <c r="V16" s="7">
+      <c r="W16" s="7">
         <v>10081</v>
       </c>
-      <c r="W16" s="5">
+      <c r="X16" s="5">
         <v>30000</v>
       </c>
-      <c r="X16" s="7">
+      <c r="Y16" s="7">
         <v>1009</v>
       </c>
-      <c r="Y16" s="5" t="s">
+      <c r="Z16" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="Z16" s="7">
+      <c r="AA16" s="7">
         <v>10021</v>
       </c>
-      <c r="AA16" s="5">
-        <v>100</v>
-      </c>
-      <c r="AB16" s="7">
+      <c r="AB16" s="5">
+        <v>100</v>
+      </c>
+      <c r="AC16" s="7">
         <v>1001</v>
       </c>
-      <c r="AC16" s="5">
-        <v>100</v>
-      </c>
-      <c r="AD16" s="7">
+      <c r="AD16" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE16" s="7">
         <v>10041</v>
       </c>
-      <c r="AE16" s="5">
-        <v>100</v>
-      </c>
-      <c r="AF16" s="7">
+      <c r="AF16" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG16" s="7">
         <v>1003</v>
       </c>
-      <c r="AG16" s="5">
+      <c r="AH16" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="2:33">
+    <row r="17" spans="2:34">
       <c r="B17" s="2">
         <v>1013</v>
       </c>
@@ -2035,112 +2096,115 @@
       <c r="D17" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="H17" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="2">
+      <c r="I17" s="2">
         <v>1010</v>
       </c>
-      <c r="I17" s="5">
+      <c r="J17" s="5">
         <v>67480</v>
       </c>
-      <c r="J17" s="5" t="s">
+      <c r="K17" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K17" s="5">
+      <c r="L17" s="5">
         <v>25900</v>
       </c>
-      <c r="L17" s="6">
+      <c r="M17" s="6">
         <v>1012</v>
       </c>
-      <c r="M17" s="5">
+      <c r="N17" s="5">
         <v>-93811</v>
       </c>
-      <c r="N17" s="6">
+      <c r="O17" s="6">
         <v>10001</v>
       </c>
-      <c r="O17" s="5">
+      <c r="P17" s="5">
         <v>2000</v>
       </c>
-      <c r="P17" s="7">
+      <c r="Q17" s="7">
         <v>10051</v>
       </c>
-      <c r="Q17" s="5">
+      <c r="R17" s="5">
         <v>2000</v>
       </c>
-      <c r="R17" s="6">
+      <c r="S17" s="6">
         <v>10061</v>
       </c>
-      <c r="S17" s="5">
+      <c r="T17" s="5">
         <v>10000</v>
       </c>
-      <c r="T17" s="7">
+      <c r="U17" s="7">
         <v>10071</v>
       </c>
-      <c r="U17" s="5">
+      <c r="V17" s="5">
         <v>500</v>
       </c>
-      <c r="V17" s="7">
+      <c r="W17" s="7">
         <v>10081</v>
       </c>
-      <c r="W17" s="5">
+      <c r="X17" s="5">
         <v>30000</v>
       </c>
-      <c r="X17" s="7">
+      <c r="Y17" s="7">
         <v>1009</v>
       </c>
-      <c r="Y17" s="5" t="s">
+      <c r="Z17" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="Z17" s="7">
+      <c r="AA17" s="7">
         <v>10021</v>
       </c>
-      <c r="AA17" s="5">
-        <v>100</v>
-      </c>
-      <c r="AB17" s="7">
+      <c r="AB17" s="5">
+        <v>100</v>
+      </c>
+      <c r="AC17" s="7">
         <v>1001</v>
       </c>
-      <c r="AC17" s="5">
-        <v>100</v>
-      </c>
-      <c r="AD17" s="7">
+      <c r="AD17" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE17" s="7">
         <v>10041</v>
       </c>
-      <c r="AE17" s="5">
-        <v>100</v>
-      </c>
-      <c r="AF17" s="7">
+      <c r="AF17" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG17" s="7">
         <v>1003</v>
       </c>
-      <c r="AG17" s="5">
+      <c r="AH17" s="5">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="H1:AG1"/>
-    <mergeCell ref="H2:AG2"/>
-    <mergeCell ref="H3:AG3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AD4:AE4"/>
-    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="I1:AH1"/>
+    <mergeCell ref="I2:AH2"/>
+    <mergeCell ref="I3:AH3"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="W4:X4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="AC4:AD4"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AG4:AH4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Packages/cn.etetet.wow/Luban/Datas/Unit.xlsx
+++ b/Packages/cn.etetet.wow/Luban/Datas/Unit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanghai/Documents/WOW/Packages/cn.etetet.wow/Luban/Datas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99876536-66FE-0F46-9375-7A65C57400E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241DA813-B7DD-084D-AB07-D61001BFAC53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4200" yWindow="4160" windowWidth="32220" windowHeight="15760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="20560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="69">
   <si>
     <t>##var</t>
   </si>
@@ -235,6 +235,18 @@
   </si>
   <si>
     <t>Map1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>出生面向</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>180</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -273,7 +285,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -298,6 +310,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -311,7 +329,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -343,6 +361,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -618,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH17"/>
+  <dimension ref="A1:AJ17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.5" customWidth="1"/>
@@ -635,24 +656,26 @@
     <col min="12" max="12" width="6.1640625" customWidth="1"/>
     <col min="13" max="13" width="5.1640625" customWidth="1"/>
     <col min="14" max="14" width="8" customWidth="1"/>
-    <col min="15" max="15" width="6.1640625" customWidth="1"/>
-    <col min="16" max="16" width="5.1640625" customWidth="1"/>
+    <col min="15" max="15" width="5.1640625" customWidth="1"/>
+    <col min="16" max="16" width="8" customWidth="1"/>
     <col min="17" max="17" width="6.1640625" customWidth="1"/>
     <col min="18" max="18" width="5.1640625" customWidth="1"/>
     <col min="19" max="19" width="6.1640625" customWidth="1"/>
-    <col min="20" max="20" width="7.1640625" customWidth="1"/>
+    <col min="20" max="20" width="5.1640625" customWidth="1"/>
     <col min="21" max="21" width="6.1640625" customWidth="1"/>
-    <col min="22" max="22" width="5.1640625" customWidth="1"/>
-    <col min="23" max="24" width="6.1640625" customWidth="1"/>
-    <col min="25" max="25" width="5.1640625" customWidth="1"/>
-    <col min="26" max="26" width="7.1640625" customWidth="1"/>
-    <col min="27" max="27" width="6.1640625" customWidth="1"/>
-    <col min="28" max="30" width="5.1640625" customWidth="1"/>
-    <col min="31" max="31" width="6.1640625" customWidth="1"/>
-    <col min="32" max="34" width="5.1640625" customWidth="1"/>
+    <col min="22" max="22" width="7.1640625" customWidth="1"/>
+    <col min="23" max="23" width="6.1640625" customWidth="1"/>
+    <col min="24" max="24" width="5.1640625" customWidth="1"/>
+    <col min="25" max="26" width="6.1640625" customWidth="1"/>
+    <col min="27" max="27" width="5.1640625" customWidth="1"/>
+    <col min="28" max="28" width="7.1640625" customWidth="1"/>
+    <col min="29" max="29" width="6.1640625" customWidth="1"/>
+    <col min="30" max="32" width="5.1640625" customWidth="1"/>
+    <col min="33" max="33" width="6.1640625" customWidth="1"/>
+    <col min="34" max="36" width="5.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:36">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -703,8 +726,10 @@
       <c r="AF1" s="8"/>
       <c r="AG1" s="8"/>
       <c r="AH1" s="8"/>
+      <c r="AI1" s="8"/>
+      <c r="AJ1" s="8"/>
     </row>
-    <row r="2" spans="1:34">
+    <row r="2" spans="1:36">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -755,8 +780,10 @@
       <c r="AF2" s="8"/>
       <c r="AG2" s="8"/>
       <c r="AH2" s="8"/>
+      <c r="AI2" s="8"/>
+      <c r="AJ2" s="8"/>
     </row>
-    <row r="3" spans="1:34">
+    <row r="3" spans="1:36">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -797,8 +824,10 @@
       <c r="AF3" s="8"/>
       <c r="AG3" s="8"/>
       <c r="AH3" s="8"/>
+      <c r="AI3" s="8"/>
+      <c r="AJ3" s="8"/>
     </row>
-    <row r="4" spans="1:34">
+    <row r="4" spans="1:36">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -835,48 +864,52 @@
         <v>23</v>
       </c>
       <c r="N4" s="9"/>
-      <c r="O4" s="10" t="s">
+      <c r="O4" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="9" t="s">
+      <c r="R4" s="10"/>
+      <c r="S4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="R4" s="9"/>
-      <c r="S4" s="10" t="s">
+      <c r="T4" s="9"/>
+      <c r="U4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="T4" s="11"/>
-      <c r="U4" s="9" t="s">
+      <c r="V4" s="11"/>
+      <c r="W4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="V4" s="12"/>
-      <c r="W4" s="10" t="s">
+      <c r="X4" s="12"/>
+      <c r="Y4" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="X4" s="11"/>
-      <c r="Y4" s="9" t="s">
+      <c r="Z4" s="11"/>
+      <c r="AA4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="Z4" s="12"/>
-      <c r="AA4" s="10" t="s">
+      <c r="AB4" s="12"/>
+      <c r="AC4" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="AB4" s="11"/>
-      <c r="AC4" s="9" t="s">
+      <c r="AD4" s="11"/>
+      <c r="AE4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="AD4" s="12"/>
-      <c r="AE4" s="10" t="s">
+      <c r="AF4" s="12"/>
+      <c r="AG4" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="AF4" s="11"/>
-      <c r="AG4" s="9" t="s">
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="AH4" s="12"/>
+      <c r="AJ4" s="12"/>
     </row>
-    <row r="5" spans="1:34">
+    <row r="5" spans="1:36">
       <c r="B5" s="2">
         <v>1001</v>
       </c>
@@ -915,67 +948,73 @@
         <v>-136000</v>
       </c>
       <c r="O5" s="6">
+        <v>1014</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q5" s="6">
         <v>10001</v>
       </c>
-      <c r="P5" s="5">
+      <c r="R5" s="5">
         <v>6000</v>
       </c>
-      <c r="Q5" s="7">
+      <c r="S5" s="7">
         <v>10051</v>
       </c>
-      <c r="R5" s="5">
+      <c r="T5" s="5">
         <v>500</v>
       </c>
-      <c r="S5" s="6">
+      <c r="U5" s="6">
         <v>10061</v>
       </c>
-      <c r="T5" s="5">
+      <c r="V5" s="5">
         <v>100000</v>
       </c>
-      <c r="U5" s="7">
+      <c r="W5" s="7">
         <v>10071</v>
       </c>
-      <c r="V5" s="5">
+      <c r="X5" s="5">
         <v>1780</v>
       </c>
-      <c r="W5" s="7">
+      <c r="Y5" s="7">
         <v>10081</v>
       </c>
-      <c r="X5" s="5">
+      <c r="Z5" s="5">
         <v>68000</v>
       </c>
-      <c r="Y5" s="7">
+      <c r="AA5" s="7">
         <v>1009</v>
       </c>
-      <c r="Z5" s="5" t="s">
+      <c r="AB5" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="AA5" s="7">
+      <c r="AC5" s="7">
         <v>10021</v>
-      </c>
-      <c r="AB5" s="5">
-        <v>1000</v>
-      </c>
-      <c r="AC5" s="7">
-        <v>1001</v>
       </c>
       <c r="AD5" s="5">
         <v>1000</v>
       </c>
       <c r="AE5" s="7">
-        <v>10041</v>
+        <v>1001</v>
       </c>
       <c r="AF5" s="5">
         <v>1000</v>
       </c>
       <c r="AG5" s="7">
-        <v>1003</v>
+        <v>10041</v>
       </c>
       <c r="AH5" s="5">
         <v>1000</v>
       </c>
+      <c r="AI5" s="7">
+        <v>1003</v>
+      </c>
+      <c r="AJ5" s="5">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="6" spans="1:34">
+    <row r="6" spans="1:36">
       <c r="B6" s="2">
         <v>1002</v>
       </c>
@@ -1016,67 +1055,73 @@
         <v>-138000</v>
       </c>
       <c r="O6" s="6">
+        <v>1014</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q6" s="6">
         <v>10001</v>
       </c>
-      <c r="P6" s="5">
+      <c r="R6" s="5">
         <v>0</v>
       </c>
-      <c r="Q6" s="7">
+      <c r="S6" s="7">
         <v>10051</v>
       </c>
-      <c r="R6" s="5">
+      <c r="T6" s="5">
         <v>500</v>
       </c>
-      <c r="S6" s="6">
+      <c r="U6" s="6">
         <v>10061</v>
       </c>
-      <c r="T6" s="5">
+      <c r="V6" s="5">
         <v>0</v>
       </c>
-      <c r="U6" s="7">
+      <c r="W6" s="7">
         <v>10071</v>
       </c>
-      <c r="V6" s="5">
+      <c r="X6" s="5">
         <v>500</v>
       </c>
-      <c r="W6" s="7">
+      <c r="Y6" s="7">
         <v>10081</v>
       </c>
-      <c r="X6" s="5">
+      <c r="Z6" s="5">
         <v>30000</v>
       </c>
-      <c r="Y6" s="7">
+      <c r="AA6" s="7">
         <v>1009</v>
       </c>
-      <c r="Z6" s="5" t="s">
+      <c r="AB6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="AA6" s="7">
+      <c r="AC6" s="7">
         <v>10021</v>
       </c>
-      <c r="AB6" s="5">
-        <v>100</v>
-      </c>
-      <c r="AC6" s="7">
+      <c r="AD6" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE6" s="7">
         <v>1001</v>
       </c>
-      <c r="AD6" s="5">
-        <v>100</v>
-      </c>
-      <c r="AE6" s="7">
+      <c r="AF6" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG6" s="7">
         <v>10041</v>
       </c>
-      <c r="AF6" s="5">
-        <v>100</v>
-      </c>
-      <c r="AG6" s="7">
+      <c r="AH6" s="5">
+        <v>100</v>
+      </c>
+      <c r="AI6" s="7">
         <v>1003</v>
       </c>
-      <c r="AH6" s="5">
+      <c r="AJ6" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:34">
+    <row r="7" spans="1:36">
       <c r="B7" s="2">
         <v>1003</v>
       </c>
@@ -1117,67 +1162,73 @@
         <v>-148001</v>
       </c>
       <c r="O7" s="6">
+        <v>1014</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q7" s="6">
         <v>10001</v>
       </c>
-      <c r="P7" s="5">
+      <c r="R7" s="5">
         <v>0</v>
       </c>
-      <c r="Q7" s="7">
+      <c r="S7" s="7">
         <v>10051</v>
       </c>
-      <c r="R7" s="5">
+      <c r="T7" s="5">
         <v>500</v>
       </c>
-      <c r="S7" s="6">
+      <c r="U7" s="6">
         <v>10061</v>
       </c>
-      <c r="T7" s="5">
+      <c r="V7" s="5">
         <v>0</v>
       </c>
-      <c r="U7" s="7">
+      <c r="W7" s="7">
         <v>10071</v>
       </c>
-      <c r="V7" s="5">
+      <c r="X7" s="5">
         <v>500</v>
       </c>
-      <c r="W7" s="7">
+      <c r="Y7" s="7">
         <v>10081</v>
       </c>
-      <c r="X7" s="5">
+      <c r="Z7" s="5">
         <v>30000</v>
       </c>
-      <c r="Y7" s="7">
+      <c r="AA7" s="7">
         <v>1009</v>
       </c>
-      <c r="Z7" s="5" t="s">
+      <c r="AB7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="AA7" s="7">
+      <c r="AC7" s="7">
         <v>10021</v>
       </c>
-      <c r="AB7" s="5">
-        <v>100</v>
-      </c>
-      <c r="AC7" s="7">
+      <c r="AD7" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE7" s="7">
         <v>1001</v>
       </c>
-      <c r="AD7" s="5">
-        <v>100</v>
-      </c>
-      <c r="AE7" s="7">
+      <c r="AF7" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG7" s="7">
         <v>10041</v>
       </c>
-      <c r="AF7" s="5">
-        <v>100</v>
-      </c>
-      <c r="AG7" s="7">
+      <c r="AH7" s="5">
+        <v>100</v>
+      </c>
+      <c r="AI7" s="7">
         <v>1003</v>
       </c>
-      <c r="AH7" s="5">
+      <c r="AJ7" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:34">
+    <row r="8" spans="1:36">
       <c r="B8" s="2">
         <v>1004</v>
       </c>
@@ -1218,67 +1269,73 @@
         <v>-58702</v>
       </c>
       <c r="O8" s="6">
+        <v>1014</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q8" s="6">
         <v>10001</v>
       </c>
-      <c r="P8" s="5">
+      <c r="R8" s="5">
         <v>2000</v>
       </c>
-      <c r="Q8" s="7">
+      <c r="S8" s="7">
         <v>10051</v>
       </c>
-      <c r="R8" s="5">
+      <c r="T8" s="5">
         <v>500</v>
       </c>
-      <c r="S8" s="6">
+      <c r="U8" s="6">
         <v>10061</v>
       </c>
-      <c r="T8" s="5">
+      <c r="V8" s="5">
         <v>10000</v>
       </c>
-      <c r="U8" s="7">
+      <c r="W8" s="7">
         <v>10071</v>
       </c>
-      <c r="V8" s="5">
+      <c r="X8" s="5">
         <v>500</v>
       </c>
-      <c r="W8" s="7">
+      <c r="Y8" s="7">
         <v>10081</v>
       </c>
-      <c r="X8" s="5">
+      <c r="Z8" s="5">
         <v>30000</v>
       </c>
-      <c r="Y8" s="7">
+      <c r="AA8" s="7">
         <v>1009</v>
       </c>
-      <c r="Z8" s="5" t="s">
+      <c r="AB8" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="AA8" s="7">
+      <c r="AC8" s="7">
         <v>10021</v>
       </c>
-      <c r="AB8" s="5">
-        <v>100</v>
-      </c>
-      <c r="AC8" s="7">
+      <c r="AD8" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE8" s="7">
         <v>1001</v>
       </c>
-      <c r="AD8" s="5">
-        <v>100</v>
-      </c>
-      <c r="AE8" s="7">
+      <c r="AF8" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG8" s="7">
         <v>10041</v>
       </c>
-      <c r="AF8" s="5">
-        <v>100</v>
-      </c>
-      <c r="AG8" s="7">
+      <c r="AH8" s="5">
+        <v>100</v>
+      </c>
+      <c r="AI8" s="7">
         <v>1003</v>
       </c>
-      <c r="AH8" s="5">
+      <c r="AJ8" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:34">
+    <row r="9" spans="1:36">
       <c r="B9" s="2">
         <v>1005</v>
       </c>
@@ -1319,67 +1376,73 @@
         <v>-23633</v>
       </c>
       <c r="O9" s="6">
+        <v>1014</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q9" s="6">
         <v>10001</v>
       </c>
-      <c r="P9" s="5">
+      <c r="R9" s="5">
         <v>2000</v>
       </c>
-      <c r="Q9" s="7">
+      <c r="S9" s="7">
         <v>10051</v>
       </c>
-      <c r="R9" s="5">
+      <c r="T9" s="5">
         <v>500</v>
       </c>
-      <c r="S9" s="6">
+      <c r="U9" s="6">
         <v>10061</v>
       </c>
-      <c r="T9" s="5">
+      <c r="V9" s="5">
         <v>10000</v>
       </c>
-      <c r="U9" s="7">
+      <c r="W9" s="7">
         <v>10071</v>
       </c>
-      <c r="V9" s="5">
+      <c r="X9" s="5">
         <v>500</v>
       </c>
-      <c r="W9" s="7">
+      <c r="Y9" s="7">
         <v>10081</v>
       </c>
-      <c r="X9" s="5">
+      <c r="Z9" s="5">
         <v>30000</v>
       </c>
-      <c r="Y9" s="7">
+      <c r="AA9" s="7">
         <v>1009</v>
       </c>
-      <c r="Z9" s="5" t="s">
+      <c r="AB9" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="AA9" s="7">
+      <c r="AC9" s="7">
         <v>10021</v>
       </c>
-      <c r="AB9" s="5">
-        <v>100</v>
-      </c>
-      <c r="AC9" s="7">
+      <c r="AD9" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE9" s="7">
         <v>1001</v>
       </c>
-      <c r="AD9" s="5">
-        <v>100</v>
-      </c>
-      <c r="AE9" s="7">
+      <c r="AF9" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG9" s="7">
         <v>10041</v>
       </c>
-      <c r="AF9" s="5">
-        <v>100</v>
-      </c>
-      <c r="AG9" s="7">
+      <c r="AH9" s="5">
+        <v>100</v>
+      </c>
+      <c r="AI9" s="7">
         <v>1003</v>
       </c>
-      <c r="AH9" s="5">
+      <c r="AJ9" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:34">
+    <row r="10" spans="1:36">
       <c r="B10" s="2">
         <v>1006</v>
       </c>
@@ -1420,67 +1483,73 @@
         <v>-23634</v>
       </c>
       <c r="O10" s="6">
+        <v>1014</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q10" s="6">
         <v>10001</v>
       </c>
-      <c r="P10" s="5">
+      <c r="R10" s="5">
         <v>2000</v>
       </c>
-      <c r="Q10" s="7">
+      <c r="S10" s="7">
         <v>10051</v>
       </c>
-      <c r="R10" s="5">
+      <c r="T10" s="5">
         <v>500</v>
       </c>
-      <c r="S10" s="6">
+      <c r="U10" s="6">
         <v>10061</v>
       </c>
-      <c r="T10" s="5">
+      <c r="V10" s="5">
         <v>10000</v>
       </c>
-      <c r="U10" s="7">
+      <c r="W10" s="7">
         <v>10071</v>
       </c>
-      <c r="V10" s="5">
+      <c r="X10" s="5">
         <v>500</v>
       </c>
-      <c r="W10" s="7">
+      <c r="Y10" s="7">
         <v>10081</v>
       </c>
-      <c r="X10" s="5">
+      <c r="Z10" s="5">
         <v>30000</v>
       </c>
-      <c r="Y10" s="7">
+      <c r="AA10" s="7">
         <v>1009</v>
       </c>
-      <c r="Z10" s="5" t="s">
+      <c r="AB10" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="AA10" s="7">
+      <c r="AC10" s="7">
         <v>10021</v>
       </c>
-      <c r="AB10" s="5">
-        <v>100</v>
-      </c>
-      <c r="AC10" s="7">
+      <c r="AD10" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE10" s="7">
         <v>1001</v>
       </c>
-      <c r="AD10" s="5">
-        <v>100</v>
-      </c>
-      <c r="AE10" s="7">
+      <c r="AF10" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG10" s="7">
         <v>10041</v>
       </c>
-      <c r="AF10" s="5">
-        <v>100</v>
-      </c>
-      <c r="AG10" s="7">
+      <c r="AH10" s="5">
+        <v>100</v>
+      </c>
+      <c r="AI10" s="7">
         <v>1003</v>
       </c>
-      <c r="AH10" s="5">
+      <c r="AJ10" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:34">
+    <row r="11" spans="1:36">
       <c r="B11" s="2">
         <v>1007</v>
       </c>
@@ -1521,67 +1590,73 @@
         <v>-40495</v>
       </c>
       <c r="O11" s="6">
+        <v>1014</v>
+      </c>
+      <c r="P11" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q11" s="6">
         <v>10001</v>
       </c>
-      <c r="P11" s="5">
+      <c r="R11" s="5">
         <v>2000</v>
       </c>
-      <c r="Q11" s="7">
+      <c r="S11" s="7">
         <v>10051</v>
       </c>
-      <c r="R11" s="5">
+      <c r="T11" s="5">
         <v>500</v>
       </c>
-      <c r="S11" s="6">
+      <c r="U11" s="6">
         <v>10061</v>
       </c>
-      <c r="T11" s="5">
+      <c r="V11" s="5">
         <v>10000</v>
       </c>
-      <c r="U11" s="7">
+      <c r="W11" s="7">
         <v>10071</v>
       </c>
-      <c r="V11" s="5">
+      <c r="X11" s="5">
         <v>500</v>
       </c>
-      <c r="W11" s="7">
+      <c r="Y11" s="7">
         <v>10081</v>
       </c>
-      <c r="X11" s="5">
+      <c r="Z11" s="5">
         <v>30000</v>
       </c>
-      <c r="Y11" s="7">
+      <c r="AA11" s="7">
         <v>1009</v>
       </c>
-      <c r="Z11" s="5" t="s">
+      <c r="AB11" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="AA11" s="7">
+      <c r="AC11" s="7">
         <v>10021</v>
       </c>
-      <c r="AB11" s="5">
-        <v>100</v>
-      </c>
-      <c r="AC11" s="7">
+      <c r="AD11" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE11" s="7">
         <v>1001</v>
       </c>
-      <c r="AD11" s="5">
-        <v>100</v>
-      </c>
-      <c r="AE11" s="7">
+      <c r="AF11" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG11" s="7">
         <v>10041</v>
       </c>
-      <c r="AF11" s="5">
-        <v>100</v>
-      </c>
-      <c r="AG11" s="7">
+      <c r="AH11" s="5">
+        <v>100</v>
+      </c>
+      <c r="AI11" s="7">
         <v>1003</v>
       </c>
-      <c r="AH11" s="5">
+      <c r="AJ11" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:34">
+    <row r="12" spans="1:36">
       <c r="B12" s="2">
         <v>1008</v>
       </c>
@@ -1622,67 +1697,73 @@
         <v>-87866</v>
       </c>
       <c r="O12" s="6">
+        <v>1014</v>
+      </c>
+      <c r="P12" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q12" s="6">
         <v>10001</v>
       </c>
-      <c r="P12" s="5">
+      <c r="R12" s="5">
         <v>2000</v>
       </c>
-      <c r="Q12" s="7">
+      <c r="S12" s="7">
         <v>10051</v>
       </c>
-      <c r="R12" s="5">
+      <c r="T12" s="5">
         <v>500</v>
       </c>
-      <c r="S12" s="6">
+      <c r="U12" s="6">
         <v>10061</v>
       </c>
-      <c r="T12" s="5">
+      <c r="V12" s="5">
         <v>10000</v>
       </c>
-      <c r="U12" s="7">
+      <c r="W12" s="7">
         <v>10071</v>
       </c>
-      <c r="V12" s="5">
+      <c r="X12" s="5">
         <v>500</v>
       </c>
-      <c r="W12" s="7">
+      <c r="Y12" s="7">
         <v>10081</v>
       </c>
-      <c r="X12" s="5">
+      <c r="Z12" s="5">
         <v>30000</v>
       </c>
-      <c r="Y12" s="7">
+      <c r="AA12" s="7">
         <v>1009</v>
       </c>
-      <c r="Z12" s="5" t="s">
+      <c r="AB12" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="AA12" s="7">
+      <c r="AC12" s="7">
         <v>10021</v>
       </c>
-      <c r="AB12" s="5">
-        <v>100</v>
-      </c>
-      <c r="AC12" s="7">
+      <c r="AD12" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE12" s="7">
         <v>1001</v>
       </c>
-      <c r="AD12" s="5">
-        <v>100</v>
-      </c>
-      <c r="AE12" s="7">
+      <c r="AF12" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG12" s="7">
         <v>10041</v>
       </c>
-      <c r="AF12" s="5">
-        <v>100</v>
-      </c>
-      <c r="AG12" s="7">
+      <c r="AH12" s="5">
+        <v>100</v>
+      </c>
+      <c r="AI12" s="7">
         <v>1003</v>
       </c>
-      <c r="AH12" s="5">
+      <c r="AJ12" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:34">
+    <row r="13" spans="1:36">
       <c r="B13" s="2">
         <v>1009</v>
       </c>
@@ -1723,67 +1804,73 @@
         <v>-141407</v>
       </c>
       <c r="O13" s="6">
+        <v>1014</v>
+      </c>
+      <c r="P13" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q13" s="6">
         <v>10001</v>
-      </c>
-      <c r="P13" s="5">
-        <v>2000</v>
-      </c>
-      <c r="Q13" s="7">
-        <v>10051</v>
       </c>
       <c r="R13" s="5">
         <v>2000</v>
       </c>
-      <c r="S13" s="6">
+      <c r="S13" s="7">
+        <v>10051</v>
+      </c>
+      <c r="T13" s="5">
+        <v>2000</v>
+      </c>
+      <c r="U13" s="6">
         <v>10061</v>
       </c>
-      <c r="T13" s="5">
+      <c r="V13" s="5">
         <v>10000</v>
       </c>
-      <c r="U13" s="7">
+      <c r="W13" s="7">
         <v>10071</v>
       </c>
-      <c r="V13" s="5">
+      <c r="X13" s="5">
         <v>500</v>
       </c>
-      <c r="W13" s="7">
+      <c r="Y13" s="7">
         <v>10081</v>
       </c>
-      <c r="X13" s="5">
+      <c r="Z13" s="5">
         <v>30000</v>
       </c>
-      <c r="Y13" s="7">
+      <c r="AA13" s="7">
         <v>1009</v>
       </c>
-      <c r="Z13" s="5" t="s">
+      <c r="AB13" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="AA13" s="7">
+      <c r="AC13" s="7">
         <v>10021</v>
       </c>
-      <c r="AB13" s="5">
-        <v>100</v>
-      </c>
-      <c r="AC13" s="7">
+      <c r="AD13" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE13" s="7">
         <v>1001</v>
       </c>
-      <c r="AD13" s="5">
-        <v>100</v>
-      </c>
-      <c r="AE13" s="7">
+      <c r="AF13" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG13" s="7">
         <v>10041</v>
       </c>
-      <c r="AF13" s="5">
-        <v>100</v>
-      </c>
-      <c r="AG13" s="7">
+      <c r="AH13" s="5">
+        <v>100</v>
+      </c>
+      <c r="AI13" s="7">
         <v>1003</v>
       </c>
-      <c r="AH13" s="5">
+      <c r="AJ13" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:34">
+    <row r="14" spans="1:36">
       <c r="B14" s="2">
         <v>1010</v>
       </c>
@@ -1824,67 +1911,73 @@
         <v>-130408</v>
       </c>
       <c r="O14" s="6">
+        <v>1014</v>
+      </c>
+      <c r="P14" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q14" s="6">
         <v>10001</v>
-      </c>
-      <c r="P14" s="5">
-        <v>2000</v>
-      </c>
-      <c r="Q14" s="7">
-        <v>10051</v>
       </c>
       <c r="R14" s="5">
         <v>2000</v>
       </c>
-      <c r="S14" s="6">
+      <c r="S14" s="7">
+        <v>10051</v>
+      </c>
+      <c r="T14" s="5">
+        <v>2000</v>
+      </c>
+      <c r="U14" s="6">
         <v>10061</v>
       </c>
-      <c r="T14" s="5">
+      <c r="V14" s="5">
         <v>10000</v>
       </c>
-      <c r="U14" s="7">
+      <c r="W14" s="7">
         <v>10071</v>
       </c>
-      <c r="V14" s="5">
+      <c r="X14" s="5">
         <v>500</v>
       </c>
-      <c r="W14" s="7">
+      <c r="Y14" s="7">
         <v>10081</v>
       </c>
-      <c r="X14" s="5">
+      <c r="Z14" s="5">
         <v>30000</v>
       </c>
-      <c r="Y14" s="7">
+      <c r="AA14" s="7">
         <v>1009</v>
       </c>
-      <c r="Z14" s="5" t="s">
+      <c r="AB14" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="AA14" s="7">
+      <c r="AC14" s="7">
         <v>10021</v>
       </c>
-      <c r="AB14" s="5">
-        <v>100</v>
-      </c>
-      <c r="AC14" s="7">
+      <c r="AD14" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE14" s="7">
         <v>1001</v>
       </c>
-      <c r="AD14" s="5">
-        <v>100</v>
-      </c>
-      <c r="AE14" s="7">
+      <c r="AF14" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG14" s="7">
         <v>10041</v>
       </c>
-      <c r="AF14" s="5">
-        <v>100</v>
-      </c>
-      <c r="AG14" s="7">
+      <c r="AH14" s="5">
+        <v>100</v>
+      </c>
+      <c r="AI14" s="7">
         <v>1003</v>
       </c>
-      <c r="AH14" s="5">
+      <c r="AJ14" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:34">
+    <row r="15" spans="1:36">
       <c r="B15" s="2">
         <v>1011</v>
       </c>
@@ -1925,67 +2018,73 @@
         <v>-130409</v>
       </c>
       <c r="O15" s="6">
+        <v>1014</v>
+      </c>
+      <c r="P15" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q15" s="6">
         <v>10001</v>
-      </c>
-      <c r="P15" s="5">
-        <v>2000</v>
-      </c>
-      <c r="Q15" s="7">
-        <v>10051</v>
       </c>
       <c r="R15" s="5">
         <v>2000</v>
       </c>
-      <c r="S15" s="6">
+      <c r="S15" s="7">
+        <v>10051</v>
+      </c>
+      <c r="T15" s="5">
+        <v>2000</v>
+      </c>
+      <c r="U15" s="6">
         <v>10061</v>
       </c>
-      <c r="T15" s="5">
+      <c r="V15" s="5">
         <v>10000</v>
       </c>
-      <c r="U15" s="7">
+      <c r="W15" s="7">
         <v>10071</v>
       </c>
-      <c r="V15" s="5">
+      <c r="X15" s="5">
         <v>500</v>
       </c>
-      <c r="W15" s="7">
+      <c r="Y15" s="7">
         <v>10081</v>
       </c>
-      <c r="X15" s="5">
+      <c r="Z15" s="5">
         <v>30000</v>
       </c>
-      <c r="Y15" s="7">
+      <c r="AA15" s="7">
         <v>1009</v>
       </c>
-      <c r="Z15" s="5" t="s">
+      <c r="AB15" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="AA15" s="7">
+      <c r="AC15" s="7">
         <v>10021</v>
       </c>
-      <c r="AB15" s="5">
-        <v>100</v>
-      </c>
-      <c r="AC15" s="7">
+      <c r="AD15" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE15" s="7">
         <v>1001</v>
       </c>
-      <c r="AD15" s="5">
-        <v>100</v>
-      </c>
-      <c r="AE15" s="7">
+      <c r="AF15" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG15" s="7">
         <v>10041</v>
       </c>
-      <c r="AF15" s="5">
-        <v>100</v>
-      </c>
-      <c r="AG15" s="7">
+      <c r="AH15" s="5">
+        <v>100</v>
+      </c>
+      <c r="AI15" s="7">
         <v>1003</v>
       </c>
-      <c r="AH15" s="5">
+      <c r="AJ15" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:34">
+    <row r="16" spans="1:36">
       <c r="B16" s="2">
         <v>1012</v>
       </c>
@@ -2026,67 +2125,73 @@
         <v>-34791</v>
       </c>
       <c r="O16" s="6">
+        <v>1014</v>
+      </c>
+      <c r="P16" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q16" s="6">
         <v>10001</v>
-      </c>
-      <c r="P16" s="5">
-        <v>2000</v>
-      </c>
-      <c r="Q16" s="7">
-        <v>10051</v>
       </c>
       <c r="R16" s="5">
         <v>2000</v>
       </c>
-      <c r="S16" s="6">
+      <c r="S16" s="7">
+        <v>10051</v>
+      </c>
+      <c r="T16" s="5">
+        <v>2000</v>
+      </c>
+      <c r="U16" s="6">
         <v>10061</v>
       </c>
-      <c r="T16" s="5">
+      <c r="V16" s="5">
         <v>10000</v>
       </c>
-      <c r="U16" s="7">
+      <c r="W16" s="7">
         <v>10071</v>
       </c>
-      <c r="V16" s="5">
+      <c r="X16" s="5">
         <v>500</v>
       </c>
-      <c r="W16" s="7">
+      <c r="Y16" s="7">
         <v>10081</v>
       </c>
-      <c r="X16" s="5">
+      <c r="Z16" s="5">
         <v>30000</v>
       </c>
-      <c r="Y16" s="7">
+      <c r="AA16" s="7">
         <v>1009</v>
       </c>
-      <c r="Z16" s="5" t="s">
+      <c r="AB16" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="AA16" s="7">
+      <c r="AC16" s="7">
         <v>10021</v>
       </c>
-      <c r="AB16" s="5">
-        <v>100</v>
-      </c>
-      <c r="AC16" s="7">
+      <c r="AD16" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE16" s="7">
         <v>1001</v>
       </c>
-      <c r="AD16" s="5">
-        <v>100</v>
-      </c>
-      <c r="AE16" s="7">
+      <c r="AF16" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG16" s="7">
         <v>10041</v>
       </c>
-      <c r="AF16" s="5">
-        <v>100</v>
-      </c>
-      <c r="AG16" s="7">
+      <c r="AH16" s="5">
+        <v>100</v>
+      </c>
+      <c r="AI16" s="7">
         <v>1003</v>
       </c>
-      <c r="AH16" s="5">
+      <c r="AJ16" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="2:34">
+    <row r="17" spans="2:36">
       <c r="B17" s="2">
         <v>1013</v>
       </c>
@@ -2127,75 +2232,81 @@
         <v>-93811</v>
       </c>
       <c r="O17" s="6">
+        <v>1014</v>
+      </c>
+      <c r="P17" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q17" s="6">
         <v>10001</v>
-      </c>
-      <c r="P17" s="5">
-        <v>2000</v>
-      </c>
-      <c r="Q17" s="7">
-        <v>10051</v>
       </c>
       <c r="R17" s="5">
         <v>2000</v>
       </c>
-      <c r="S17" s="6">
+      <c r="S17" s="7">
+        <v>10051</v>
+      </c>
+      <c r="T17" s="5">
+        <v>2000</v>
+      </c>
+      <c r="U17" s="6">
         <v>10061</v>
       </c>
-      <c r="T17" s="5">
+      <c r="V17" s="5">
         <v>10000</v>
       </c>
-      <c r="U17" s="7">
+      <c r="W17" s="7">
         <v>10071</v>
       </c>
-      <c r="V17" s="5">
+      <c r="X17" s="5">
         <v>500</v>
       </c>
-      <c r="W17" s="7">
+      <c r="Y17" s="7">
         <v>10081</v>
       </c>
-      <c r="X17" s="5">
+      <c r="Z17" s="5">
         <v>30000</v>
       </c>
-      <c r="Y17" s="7">
+      <c r="AA17" s="7">
         <v>1009</v>
       </c>
-      <c r="Z17" s="5" t="s">
+      <c r="AB17" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="AA17" s="7">
+      <c r="AC17" s="7">
         <v>10021</v>
       </c>
-      <c r="AB17" s="5">
-        <v>100</v>
-      </c>
-      <c r="AC17" s="7">
+      <c r="AD17" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE17" s="7">
         <v>1001</v>
       </c>
-      <c r="AD17" s="5">
-        <v>100</v>
-      </c>
-      <c r="AE17" s="7">
+      <c r="AF17" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG17" s="7">
         <v>10041</v>
       </c>
-      <c r="AF17" s="5">
-        <v>100</v>
-      </c>
-      <c r="AG17" s="7">
+      <c r="AH17" s="5">
+        <v>100</v>
+      </c>
+      <c r="AI17" s="7">
         <v>1003</v>
       </c>
-      <c r="AH17" s="5">
+      <c r="AJ17" s="5">
         <v>100</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="I1:AH1"/>
-    <mergeCell ref="I2:AH2"/>
-    <mergeCell ref="I3:AH3"/>
+  <mergeCells count="17">
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="I1:AJ1"/>
+    <mergeCell ref="I2:AJ2"/>
+    <mergeCell ref="I3:AJ3"/>
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:P4"/>
     <mergeCell ref="Q4:R4"/>
     <mergeCell ref="S4:T4"/>
     <mergeCell ref="U4:V4"/>
@@ -2205,6 +2316,7 @@
     <mergeCell ref="AC4:AD4"/>
     <mergeCell ref="AE4:AF4"/>
     <mergeCell ref="AG4:AH4"/>
+    <mergeCell ref="AI4:AJ4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Packages/cn.etetet.wow/Luban/Datas/Unit.xlsx
+++ b/Packages/cn.etetet.wow/Luban/Datas/Unit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanghai/Documents/WOW/Packages/cn.etetet.wow/Luban/Datas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241DA813-B7DD-084D-AB07-D61001BFAC53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{275D38C0-41B9-E642-B12C-574242A24A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="20560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="65">
   <si>
     <t>##var</t>
   </si>
@@ -149,15 +149,6 @@
     <t>法师</t>
   </si>
   <si>
-    <t>56000</t>
-  </si>
-  <si>
-    <t>1011</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>Monster</t>
   </si>
   <si>
@@ -183,9 +174,6 @@
   </si>
   <si>
     <t>德鲁伊</t>
-  </si>
-  <si>
-    <t>300000</t>
   </si>
   <si>
     <t>猎人</t>
@@ -242,11 +230,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>0</t>
+    <t>Map2</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>180</t>
+    <t>Virtual</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -329,7 +317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -350,6 +338,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -361,8 +352,8 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -689,7 +680,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1" t="s">
@@ -698,36 +689,36 @@
       <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="V1" s="8"/>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="8"/>
-      <c r="Z1" s="8"/>
-      <c r="AA1" s="8"/>
-      <c r="AB1" s="8"/>
-      <c r="AC1" s="8"/>
-      <c r="AD1" s="8"/>
-      <c r="AE1" s="8"/>
-      <c r="AF1" s="8"/>
-      <c r="AG1" s="8"/>
-      <c r="AH1" s="8"/>
-      <c r="AI1" s="8"/>
-      <c r="AJ1" s="8"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="9"/>
+      <c r="AG1" s="9"/>
+      <c r="AH1" s="9"/>
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="9"/>
     </row>
     <row r="2" spans="1:36">
       <c r="A2" t="s">
@@ -743,7 +734,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
@@ -752,36 +743,36 @@
       <c r="H2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
-      <c r="V2" s="8"/>
-      <c r="W2" s="8"/>
-      <c r="X2" s="8"/>
-      <c r="Y2" s="8"/>
-      <c r="Z2" s="8"/>
-      <c r="AA2" s="8"/>
-      <c r="AB2" s="8"/>
-      <c r="AC2" s="8"/>
-      <c r="AD2" s="8"/>
-      <c r="AE2" s="8"/>
-      <c r="AF2" s="8"/>
-      <c r="AG2" s="8"/>
-      <c r="AH2" s="8"/>
-      <c r="AI2" s="8"/>
-      <c r="AJ2" s="8"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="9"/>
+      <c r="AE2" s="9"/>
+      <c r="AF2" s="9"/>
+      <c r="AG2" s="9"/>
+      <c r="AH2" s="9"/>
+      <c r="AI2" s="9"/>
+      <c r="AJ2" s="9"/>
     </row>
     <row r="3" spans="1:36">
       <c r="A3" t="s">
@@ -796,36 +787,36 @@
         <v>13</v>
       </c>
       <c r="H3" s="1"/>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="8"/>
-      <c r="W3" s="8"/>
-      <c r="X3" s="8"/>
-      <c r="Y3" s="8"/>
-      <c r="Z3" s="8"/>
-      <c r="AA3" s="8"/>
-      <c r="AB3" s="8"/>
-      <c r="AC3" s="8"/>
-      <c r="AD3" s="8"/>
-      <c r="AE3" s="8"/>
-      <c r="AF3" s="8"/>
-      <c r="AG3" s="8"/>
-      <c r="AH3" s="8"/>
-      <c r="AI3" s="8"/>
-      <c r="AJ3" s="8"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="9"/>
+      <c r="AE3" s="9"/>
+      <c r="AF3" s="9"/>
+      <c r="AG3" s="9"/>
+      <c r="AH3" s="9"/>
+      <c r="AI3" s="9"/>
+      <c r="AJ3" s="9"/>
     </row>
     <row r="4" spans="1:36">
       <c r="A4" t="s">
@@ -841,7 +832,7 @@
         <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>18</v>
@@ -852,69 +843,69 @@
       <c r="H4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="9"/>
-      <c r="K4" s="10" t="s">
+      <c r="J4" s="10"/>
+      <c r="K4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="L4" s="10"/>
-      <c r="M4" s="9" t="s">
+      <c r="L4" s="11"/>
+      <c r="M4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="N4" s="9"/>
-      <c r="O4" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="10" t="s">
+      <c r="N4" s="10"/>
+      <c r="O4" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="R4" s="10"/>
-      <c r="S4" s="9" t="s">
+      <c r="R4" s="11"/>
+      <c r="S4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="T4" s="9"/>
-      <c r="U4" s="10" t="s">
+      <c r="T4" s="10"/>
+      <c r="U4" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="V4" s="11"/>
-      <c r="W4" s="9" t="s">
+      <c r="V4" s="12"/>
+      <c r="W4" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="X4" s="12"/>
-      <c r="Y4" s="10" t="s">
+      <c r="X4" s="13"/>
+      <c r="Y4" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="Z4" s="11"/>
-      <c r="AA4" s="9" t="s">
+      <c r="Z4" s="12"/>
+      <c r="AA4" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="AB4" s="12"/>
-      <c r="AC4" s="10" t="s">
+      <c r="AB4" s="13"/>
+      <c r="AC4" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="AD4" s="11"/>
-      <c r="AE4" s="9" t="s">
+      <c r="AD4" s="12"/>
+      <c r="AE4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="AF4" s="12"/>
-      <c r="AG4" s="10" t="s">
+      <c r="AF4" s="13"/>
+      <c r="AG4" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="AH4" s="11"/>
-      <c r="AI4" s="9" t="s">
+      <c r="AH4" s="12"/>
+      <c r="AI4" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AJ4" s="12"/>
+      <c r="AJ4" s="13"/>
     </row>
     <row r="5" spans="1:36">
       <c r="B5" s="2">
         <v>1001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>34</v>
@@ -932,26 +923,26 @@
       <c r="I5" s="2">
         <v>1010</v>
       </c>
-      <c r="J5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="L5" s="5">
-        <v>29000</v>
+      <c r="J5" s="14">
+        <v>3000</v>
+      </c>
+      <c r="K5" s="14">
+        <v>1011</v>
+      </c>
+      <c r="L5" s="14">
+        <v>25200</v>
       </c>
       <c r="M5" s="6">
         <v>1012</v>
       </c>
-      <c r="N5" s="5">
-        <v>-136000</v>
+      <c r="N5" s="14">
+        <v>3000</v>
       </c>
       <c r="O5" s="6">
         <v>1014</v>
       </c>
-      <c r="P5" s="5" t="s">
-        <v>67</v>
+      <c r="P5" s="14">
+        <v>0</v>
       </c>
       <c r="Q5" s="6">
         <v>10001</v>
@@ -986,8 +977,8 @@
       <c r="AA5" s="7">
         <v>1009</v>
       </c>
-      <c r="AB5" s="5" t="s">
-        <v>40</v>
+      <c r="AB5" s="14">
+        <v>0</v>
       </c>
       <c r="AC5" s="7">
         <v>10021</v>
@@ -1019,46 +1010,46 @@
         <v>1002</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="H6" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="I6" s="2">
         <v>1010</v>
       </c>
-      <c r="J6" s="5">
-        <v>56000</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="L6" s="5">
-        <v>30000</v>
+      <c r="J6" s="14">
+        <v>0</v>
+      </c>
+      <c r="K6" s="14">
+        <v>1011</v>
+      </c>
+      <c r="L6" s="14">
+        <v>25200</v>
       </c>
       <c r="M6" s="6">
         <v>1012</v>
       </c>
-      <c r="N6" s="5">
-        <v>-138000</v>
+      <c r="N6" s="14">
+        <v>0</v>
       </c>
       <c r="O6" s="6">
         <v>1014</v>
       </c>
-      <c r="P6" s="5" t="s">
-        <v>67</v>
+      <c r="P6" s="14">
+        <v>90</v>
       </c>
       <c r="Q6" s="6">
         <v>10001</v>
@@ -1093,8 +1084,8 @@
       <c r="AA6" s="7">
         <v>1009</v>
       </c>
-      <c r="AB6" s="5" t="s">
-        <v>40</v>
+      <c r="AB6" s="14">
+        <v>300003</v>
       </c>
       <c r="AC6" s="7">
         <v>10021</v>
@@ -1126,46 +1117,46 @@
         <v>1003</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="H7" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="I7" s="2">
         <v>1010</v>
       </c>
-      <c r="J7" s="5">
-        <v>58740</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="L7" s="5">
-        <v>29090</v>
+      <c r="J7" s="14">
+        <v>0</v>
+      </c>
+      <c r="K7" s="14">
+        <v>1011</v>
+      </c>
+      <c r="L7" s="14">
+        <v>25200</v>
       </c>
       <c r="M7" s="6">
         <v>1012</v>
       </c>
-      <c r="N7" s="5">
-        <v>-148001</v>
+      <c r="N7" s="14">
+        <v>0</v>
       </c>
       <c r="O7" s="6">
         <v>1014</v>
       </c>
-      <c r="P7" s="5" t="s">
-        <v>68</v>
+      <c r="P7" s="14">
+        <v>270</v>
       </c>
       <c r="Q7" s="6">
         <v>10001</v>
@@ -1200,8 +1191,8 @@
       <c r="AA7" s="7">
         <v>1009</v>
       </c>
-      <c r="AB7" s="5" t="s">
-        <v>40</v>
+      <c r="AB7" s="14">
+        <v>300003</v>
       </c>
       <c r="AC7" s="7">
         <v>10021</v>
@@ -1233,22 +1224,22 @@
         <v>1004</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="H8" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I8" s="2">
         <v>1010</v>
@@ -1256,8 +1247,8 @@
       <c r="J8" s="5">
         <v>21600</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>39</v>
+      <c r="K8" s="14">
+        <v>1011</v>
       </c>
       <c r="L8" s="5">
         <v>26800</v>
@@ -1271,8 +1262,8 @@
       <c r="O8" s="6">
         <v>1014</v>
       </c>
-      <c r="P8" s="5" t="s">
-        <v>67</v>
+      <c r="P8" s="14">
+        <v>0</v>
       </c>
       <c r="Q8" s="6">
         <v>10001</v>
@@ -1307,8 +1298,8 @@
       <c r="AA8" s="7">
         <v>1009</v>
       </c>
-      <c r="AB8" s="5" t="s">
-        <v>50</v>
+      <c r="AB8" s="14">
+        <v>300000</v>
       </c>
       <c r="AC8" s="7">
         <v>10021</v>
@@ -1340,22 +1331,22 @@
         <v>1005</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="H9" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="I9" s="2">
         <v>1010</v>
@@ -1363,8 +1354,8 @@
       <c r="J9" s="5">
         <v>56000</v>
       </c>
-      <c r="K9" s="5" t="s">
-        <v>39</v>
+      <c r="K9" s="14">
+        <v>1011</v>
       </c>
       <c r="L9" s="5">
         <v>25180</v>
@@ -1378,8 +1369,8 @@
       <c r="O9" s="6">
         <v>1014</v>
       </c>
-      <c r="P9" s="5" t="s">
-        <v>67</v>
+      <c r="P9" s="14">
+        <v>0</v>
       </c>
       <c r="Q9" s="6">
         <v>10001</v>
@@ -1414,8 +1405,8 @@
       <c r="AA9" s="7">
         <v>1009</v>
       </c>
-      <c r="AB9" s="5" t="s">
-        <v>50</v>
+      <c r="AB9" s="14">
+        <v>300000</v>
       </c>
       <c r="AC9" s="7">
         <v>10021</v>
@@ -1447,19 +1438,19 @@
         <v>1006</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>37</v>
@@ -1470,8 +1461,8 @@
       <c r="J10" s="5">
         <v>36310</v>
       </c>
-      <c r="K10" s="5" t="s">
-        <v>39</v>
+      <c r="K10" s="14">
+        <v>1011</v>
       </c>
       <c r="L10" s="5">
         <v>25180</v>
@@ -1485,8 +1476,8 @@
       <c r="O10" s="6">
         <v>1014</v>
       </c>
-      <c r="P10" s="5" t="s">
-        <v>67</v>
+      <c r="P10" s="14">
+        <v>0</v>
       </c>
       <c r="Q10" s="6">
         <v>10001</v>
@@ -1521,8 +1512,8 @@
       <c r="AA10" s="7">
         <v>1009</v>
       </c>
-      <c r="AB10" s="5" t="s">
-        <v>50</v>
+      <c r="AB10" s="14">
+        <v>300000</v>
       </c>
       <c r="AC10" s="7">
         <v>10021</v>
@@ -1554,22 +1545,22 @@
         <v>1007</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="H11" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="I11" s="2">
         <v>1010</v>
@@ -1577,8 +1568,8 @@
       <c r="J11" s="5">
         <v>67170</v>
       </c>
-      <c r="K11" s="5" t="s">
-        <v>39</v>
+      <c r="K11" s="14">
+        <v>1011</v>
       </c>
       <c r="L11" s="5">
         <v>25180</v>
@@ -1592,8 +1583,8 @@
       <c r="O11" s="6">
         <v>1014</v>
       </c>
-      <c r="P11" s="5" t="s">
-        <v>67</v>
+      <c r="P11" s="14">
+        <v>0</v>
       </c>
       <c r="Q11" s="6">
         <v>10001</v>
@@ -1628,8 +1619,8 @@
       <c r="AA11" s="7">
         <v>1009</v>
       </c>
-      <c r="AB11" s="5" t="s">
-        <v>50</v>
+      <c r="AB11" s="14">
+        <v>300000</v>
       </c>
       <c r="AC11" s="7">
         <v>10021</v>
@@ -1661,22 +1652,22 @@
         <v>1008</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="H12" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I12" s="2">
         <v>1010</v>
@@ -1684,8 +1675,8 @@
       <c r="J12" s="5">
         <v>59600</v>
       </c>
-      <c r="K12" s="5" t="s">
-        <v>39</v>
+      <c r="K12" s="14">
+        <v>1011</v>
       </c>
       <c r="L12" s="5">
         <v>25800</v>
@@ -1699,8 +1690,8 @@
       <c r="O12" s="6">
         <v>1014</v>
       </c>
-      <c r="P12" s="5" t="s">
-        <v>67</v>
+      <c r="P12" s="14">
+        <v>0</v>
       </c>
       <c r="Q12" s="6">
         <v>10001</v>
@@ -1735,8 +1726,8 @@
       <c r="AA12" s="7">
         <v>1009</v>
       </c>
-      <c r="AB12" s="5" t="s">
-        <v>50</v>
+      <c r="AB12" s="14">
+        <v>300000</v>
       </c>
       <c r="AC12" s="7">
         <v>10021</v>
@@ -1768,22 +1759,22 @@
         <v>1009</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="H13" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I13" s="2">
         <v>1010</v>
@@ -1791,8 +1782,8 @@
       <c r="J13" s="5">
         <v>58740</v>
       </c>
-      <c r="K13" s="5" t="s">
-        <v>39</v>
+      <c r="K13" s="14">
+        <v>1011</v>
       </c>
       <c r="L13" s="5">
         <v>28100</v>
@@ -1806,8 +1797,8 @@
       <c r="O13" s="6">
         <v>1014</v>
       </c>
-      <c r="P13" s="5" t="s">
-        <v>67</v>
+      <c r="P13" s="14">
+        <v>0</v>
       </c>
       <c r="Q13" s="6">
         <v>10001</v>
@@ -1842,8 +1833,8 @@
       <c r="AA13" s="7">
         <v>1009</v>
       </c>
-      <c r="AB13" s="5" t="s">
-        <v>50</v>
+      <c r="AB13" s="14">
+        <v>300000</v>
       </c>
       <c r="AC13" s="7">
         <v>10021</v>
@@ -1875,22 +1866,22 @@
         <v>1010</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="H14" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I14" s="2">
         <v>1010</v>
@@ -1898,8 +1889,8 @@
       <c r="J14" s="5">
         <v>58740</v>
       </c>
-      <c r="K14" s="5" t="s">
-        <v>39</v>
+      <c r="K14" s="14">
+        <v>1011</v>
       </c>
       <c r="L14" s="5">
         <v>28100</v>
@@ -1913,8 +1904,8 @@
       <c r="O14" s="6">
         <v>1014</v>
       </c>
-      <c r="P14" s="5" t="s">
-        <v>67</v>
+      <c r="P14" s="14">
+        <v>0</v>
       </c>
       <c r="Q14" s="6">
         <v>10001</v>
@@ -1949,8 +1940,8 @@
       <c r="AA14" s="7">
         <v>1009</v>
       </c>
-      <c r="AB14" s="5" t="s">
-        <v>50</v>
+      <c r="AB14" s="14">
+        <v>300000</v>
       </c>
       <c r="AC14" s="7">
         <v>10021</v>
@@ -1982,22 +1973,22 @@
         <v>1011</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="H15" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>58</v>
       </c>
       <c r="I15" s="2">
         <v>1010</v>
@@ -2005,8 +1996,8 @@
       <c r="J15" s="5">
         <v>67480</v>
       </c>
-      <c r="K15" s="5" t="s">
-        <v>39</v>
+      <c r="K15" s="14">
+        <v>1011</v>
       </c>
       <c r="L15" s="5">
         <v>28850</v>
@@ -2020,8 +2011,8 @@
       <c r="O15" s="6">
         <v>1014</v>
       </c>
-      <c r="P15" s="5" t="s">
-        <v>67</v>
+      <c r="P15" s="14">
+        <v>0</v>
       </c>
       <c r="Q15" s="6">
         <v>10001</v>
@@ -2056,8 +2047,8 @@
       <c r="AA15" s="7">
         <v>1009</v>
       </c>
-      <c r="AB15" s="5" t="s">
-        <v>50</v>
+      <c r="AB15" s="14">
+        <v>300000</v>
       </c>
       <c r="AC15" s="7">
         <v>10021</v>
@@ -2089,22 +2080,22 @@
         <v>1012</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="H16" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="I16" s="2">
         <v>1010</v>
@@ -2112,8 +2103,8 @@
       <c r="J16" s="5">
         <v>67480</v>
       </c>
-      <c r="K16" s="5" t="s">
-        <v>39</v>
+      <c r="K16" s="14">
+        <v>1011</v>
       </c>
       <c r="L16" s="5">
         <v>27510</v>
@@ -2127,8 +2118,8 @@
       <c r="O16" s="6">
         <v>1014</v>
       </c>
-      <c r="P16" s="5" t="s">
-        <v>67</v>
+      <c r="P16" s="14">
+        <v>0</v>
       </c>
       <c r="Q16" s="6">
         <v>10001</v>
@@ -2163,8 +2154,8 @@
       <c r="AA16" s="7">
         <v>1009</v>
       </c>
-      <c r="AB16" s="5" t="s">
-        <v>50</v>
+      <c r="AB16" s="14">
+        <v>300000</v>
       </c>
       <c r="AC16" s="7">
         <v>10021</v>
@@ -2196,22 +2187,22 @@
         <v>1013</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="H17" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I17" s="2">
         <v>1010</v>
@@ -2219,8 +2210,8 @@
       <c r="J17" s="5">
         <v>67480</v>
       </c>
-      <c r="K17" s="5" t="s">
-        <v>39</v>
+      <c r="K17" s="14">
+        <v>1011</v>
       </c>
       <c r="L17" s="5">
         <v>25900</v>
@@ -2234,8 +2225,8 @@
       <c r="O17" s="6">
         <v>1014</v>
       </c>
-      <c r="P17" s="5" t="s">
-        <v>67</v>
+      <c r="P17" s="14">
+        <v>0</v>
       </c>
       <c r="Q17" s="6">
         <v>10001</v>
@@ -2270,8 +2261,8 @@
       <c r="AA17" s="7">
         <v>1009</v>
       </c>
-      <c r="AB17" s="5" t="s">
-        <v>50</v>
+      <c r="AB17" s="14">
+        <v>300000</v>
       </c>
       <c r="AC17" s="7">
         <v>10021</v>
@@ -2300,6 +2291,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AI4:AJ4"/>
     <mergeCell ref="O4:P4"/>
     <mergeCell ref="I1:AJ1"/>
     <mergeCell ref="I2:AJ2"/>
@@ -2316,7 +2308,6 @@
     <mergeCell ref="AC4:AD4"/>
     <mergeCell ref="AE4:AF4"/>
     <mergeCell ref="AG4:AH4"/>
-    <mergeCell ref="AI4:AJ4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Packages/cn.etetet.wow/Luban/Datas/Unit.xlsx
+++ b/Packages/cn.etetet.wow/Luban/Datas/Unit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanghai/Documents/WOW/Packages/cn.etetet.wow/Luban/Datas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{275D38C0-41B9-E642-B12C-574242A24A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D75F70B3-E7A0-C044-937D-BDE54D7498DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="20560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -924,7 +924,7 @@
         <v>1010</v>
       </c>
       <c r="J5" s="14">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="K5" s="14">
         <v>1011</v>
@@ -936,7 +936,7 @@
         <v>1012</v>
       </c>
       <c r="N5" s="14">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="O5" s="6">
         <v>1014</v>
@@ -1043,7 +1043,7 @@
         <v>1012</v>
       </c>
       <c r="N6" s="14">
-        <v>0</v>
+        <v>-50000</v>
       </c>
       <c r="O6" s="6">
         <v>1014</v>
